--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R487"/>
+  <dimension ref="A1:R488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29660,6 +29660,66 @@
       <c r="R487" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="n">
+        <v>290.55</v>
+      </c>
+      <c r="C488" t="n">
+        <v>278.66</v>
+      </c>
+      <c r="D488" t="n">
+        <v>286.42</v>
+      </c>
+      <c r="E488" t="n">
+        <v>300.19</v>
+      </c>
+      <c r="F488" t="n">
+        <v>298.73</v>
+      </c>
+      <c r="G488" t="n">
+        <v>294.95</v>
+      </c>
+      <c r="H488" t="n">
+        <v>288.56</v>
+      </c>
+      <c r="I488" t="n">
+        <v>261.79</v>
+      </c>
+      <c r="J488" t="n">
+        <v>250.24</v>
+      </c>
+      <c r="K488" t="n">
+        <v>251.43</v>
+      </c>
+      <c r="L488" t="n">
+        <v>255.5</v>
+      </c>
+      <c r="M488" t="n">
+        <v>263.98</v>
+      </c>
+      <c r="N488" t="n">
+        <v>267.75</v>
+      </c>
+      <c r="O488" t="n">
+        <v>276.55</v>
+      </c>
+      <c r="P488" t="n">
+        <v>291.26</v>
+      </c>
+      <c r="Q488" t="n">
+        <v>299.18</v>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -29674,7 +29734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B517"/>
+  <dimension ref="A1:B518"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34847,6 +34907,16 @@
       </c>
       <c r="B517" t="n">
         <v>-0.2</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B518" t="n">
+        <v>0.08</v>
       </c>
     </row>
   </sheetData>
@@ -35015,28 +35085,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04991545981279102</v>
+        <v>-0.05093920733945623</v>
       </c>
       <c r="J2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K2" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001454400100880715</v>
+        <v>0.001521032254514831</v>
       </c>
       <c r="M2" t="n">
-        <v>7.876208338832459</v>
+        <v>7.865008571098281</v>
       </c>
       <c r="N2" t="n">
-        <v>94.64991662771767</v>
+        <v>94.46875167724012</v>
       </c>
       <c r="O2" t="n">
-        <v>9.728818871153768</v>
+        <v>9.719503674429067</v>
       </c>
       <c r="P2" t="n">
-        <v>294.4101938410124</v>
+        <v>294.4208338226293</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35093,28 +35163,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3815541234731679</v>
+        <v>-0.3839691379196973</v>
       </c>
       <c r="J3" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K3" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0367201679169652</v>
+        <v>0.03731454287306302</v>
       </c>
       <c r="M3" t="n">
-        <v>11.92544863303013</v>
+        <v>11.91371180241367</v>
       </c>
       <c r="N3" t="n">
-        <v>210.030757519673</v>
+        <v>209.6696692084221</v>
       </c>
       <c r="O3" t="n">
-        <v>14.49243794258485</v>
+        <v>14.4799747654622</v>
       </c>
       <c r="P3" t="n">
-        <v>294.6769687279282</v>
+        <v>294.7022206940215</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35171,28 +35241,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6580594928184091</v>
+        <v>-0.6584493203406335</v>
       </c>
       <c r="J4" t="n">
+        <v>487</v>
+      </c>
+      <c r="K4" t="n">
         <v>486</v>
       </c>
-      <c r="K4" t="n">
-        <v>485</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1398725838736413</v>
+        <v>0.1405434458921301</v>
       </c>
       <c r="M4" t="n">
-        <v>9.77097367972628</v>
+        <v>9.753482378099733</v>
       </c>
       <c r="N4" t="n">
-        <v>147.5408151108075</v>
+        <v>147.2391497944616</v>
       </c>
       <c r="O4" t="n">
-        <v>12.14663801678503</v>
+        <v>12.13421401634493</v>
       </c>
       <c r="P4" t="n">
-        <v>304.7364817173565</v>
+        <v>304.7405324621331</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35249,28 +35319,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2563163447298781</v>
+        <v>-0.2553927588894865</v>
       </c>
       <c r="J5" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K5" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08950663756129251</v>
+        <v>0.08925329289126205</v>
       </c>
       <c r="M5" t="n">
-        <v>4.216444764412615</v>
+        <v>4.211957910479698</v>
       </c>
       <c r="N5" t="n">
-        <v>36.97772777524228</v>
+        <v>36.91253185678694</v>
       </c>
       <c r="O5" t="n">
-        <v>6.080931489109402</v>
+        <v>6.075568438984696</v>
       </c>
       <c r="P5" t="n">
-        <v>304.6525820412739</v>
+        <v>304.6429830570444</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35327,28 +35397,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3189235616295726</v>
+        <v>-0.3177120608606369</v>
       </c>
       <c r="J6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K6" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1964410778582685</v>
+        <v>0.1958076456149268</v>
       </c>
       <c r="M6" t="n">
-        <v>3.538457422675268</v>
+        <v>3.537439358571358</v>
       </c>
       <c r="N6" t="n">
-        <v>23.02102769819027</v>
+        <v>22.99222556115983</v>
       </c>
       <c r="O6" t="n">
-        <v>4.79802331155136</v>
+        <v>4.795020913526846</v>
       </c>
       <c r="P6" t="n">
-        <v>304.1276195228031</v>
+        <v>304.1150281899063</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35405,28 +35475,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3347619694035069</v>
+        <v>-0.3345450240153361</v>
       </c>
       <c r="J7" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K7" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3048536674227118</v>
+        <v>0.3055023669315858</v>
       </c>
       <c r="M7" t="n">
-        <v>2.904859261983932</v>
+        <v>2.900137995169169</v>
       </c>
       <c r="N7" t="n">
-        <v>14.13914399452934</v>
+        <v>14.11070308236186</v>
       </c>
       <c r="O7" t="n">
-        <v>3.760205312815955</v>
+        <v>3.756421579423942</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2399680068654</v>
+        <v>303.2377132566639</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35483,28 +35553,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4507295690490622</v>
+        <v>-0.4512258992902541</v>
       </c>
       <c r="J8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K8" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3864650559612252</v>
+        <v>0.3879895593090227</v>
       </c>
       <c r="M8" t="n">
-        <v>3.26525532781943</v>
+        <v>3.260867982897286</v>
       </c>
       <c r="N8" t="n">
-        <v>17.84543952197076</v>
+        <v>17.81189573054201</v>
       </c>
       <c r="O8" t="n">
-        <v>4.224386289388171</v>
+        <v>4.220414165759329</v>
       </c>
       <c r="P8" t="n">
-        <v>301.6767465231815</v>
+        <v>301.681904967529</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35561,28 +35631,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2752283564762056</v>
+        <v>-0.2795069059166965</v>
       </c>
       <c r="J9" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K9" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01188056614997357</v>
+        <v>0.01229391641191846</v>
       </c>
       <c r="M9" t="n">
-        <v>13.97706082532322</v>
+        <v>13.97046711263209</v>
       </c>
       <c r="N9" t="n">
-        <v>343.8072149132425</v>
+        <v>343.3241161701031</v>
       </c>
       <c r="O9" t="n">
-        <v>18.54203912500571</v>
+        <v>18.52900742538852</v>
       </c>
       <c r="P9" t="n">
-        <v>279.5497264934211</v>
+        <v>279.5946395149554</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35639,28 +35709,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3657269953553768</v>
+        <v>-0.3703393426143782</v>
       </c>
       <c r="J10" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K10" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02188475558344749</v>
+        <v>0.02250655710514993</v>
       </c>
       <c r="M10" t="n">
-        <v>13.71389816869594</v>
+        <v>13.7070421125959</v>
       </c>
       <c r="N10" t="n">
-        <v>330.7717723738136</v>
+        <v>330.3602639111496</v>
       </c>
       <c r="O10" t="n">
-        <v>18.18713205466474</v>
+        <v>18.17581535753347</v>
       </c>
       <c r="P10" t="n">
-        <v>271.3416551247248</v>
+        <v>271.3895920317927</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35717,28 +35787,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4174411995203301</v>
+        <v>-0.4216374390584161</v>
       </c>
       <c r="J11" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K11" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03340644960991679</v>
+        <v>0.03417725613103495</v>
       </c>
       <c r="M11" t="n">
-        <v>12.48401724611558</v>
+        <v>12.48042406814468</v>
       </c>
       <c r="N11" t="n">
-        <v>276.7376545697773</v>
+        <v>276.3843718156426</v>
       </c>
       <c r="O11" t="n">
-        <v>16.63543370549074</v>
+        <v>16.62481193324131</v>
       </c>
       <c r="P11" t="n">
-        <v>272.7661667338355</v>
+        <v>272.8101420560832</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35795,28 +35865,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5601722573365034</v>
+        <v>-0.5635224622924013</v>
       </c>
       <c r="J12" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K12" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1481832283073908</v>
+        <v>0.1500746845365575</v>
       </c>
       <c r="M12" t="n">
-        <v>7.327685646272472</v>
+        <v>7.334785776200715</v>
       </c>
       <c r="N12" t="n">
-        <v>99.80594359095087</v>
+        <v>99.74223683648746</v>
       </c>
       <c r="O12" t="n">
-        <v>9.990292467738414</v>
+        <v>9.987103525872127</v>
       </c>
       <c r="P12" t="n">
-        <v>278.5934764126609</v>
+        <v>278.6282956607816</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35873,28 +35943,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2363729232815042</v>
+        <v>-0.236914240196816</v>
       </c>
       <c r="J13" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K13" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05044111069732782</v>
+        <v>0.05086954817813427</v>
       </c>
       <c r="M13" t="n">
-        <v>5.847606513370803</v>
+        <v>5.838650294277969</v>
       </c>
       <c r="N13" t="n">
-        <v>58.19675808918717</v>
+        <v>58.08094477383561</v>
       </c>
       <c r="O13" t="n">
-        <v>7.628679970295462</v>
+        <v>7.621085537758752</v>
       </c>
       <c r="P13" t="n">
-        <v>271.5604297177129</v>
+        <v>271.5660557161918</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35951,28 +36021,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1082781981791369</v>
+        <v>0.1079810955544874</v>
       </c>
       <c r="J14" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K14" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01133407822358745</v>
+        <v>0.0113215661004793</v>
       </c>
       <c r="M14" t="n">
-        <v>5.945795506469341</v>
+        <v>5.935212647866041</v>
       </c>
       <c r="N14" t="n">
-        <v>56.58632332929913</v>
+        <v>56.47124037611464</v>
       </c>
       <c r="O14" t="n">
-        <v>7.522388140032334</v>
+        <v>7.514734883953967</v>
       </c>
       <c r="P14" t="n">
-        <v>265.6281320682901</v>
+        <v>265.6312199062407</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36029,28 +36099,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3981041732825216</v>
+        <v>0.3990554683199034</v>
       </c>
       <c r="J15" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K15" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1325073607629177</v>
+        <v>0.1335421420819565</v>
       </c>
       <c r="M15" t="n">
-        <v>5.813304893819566</v>
+        <v>5.805870189467774</v>
       </c>
       <c r="N15" t="n">
-        <v>57.40970725224961</v>
+        <v>57.30321027207936</v>
       </c>
       <c r="O15" t="n">
-        <v>7.576919377441574</v>
+        <v>7.569888392313282</v>
       </c>
       <c r="P15" t="n">
-        <v>263.6868228415496</v>
+        <v>263.6769358709378</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36107,28 +36177,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4423104261529941</v>
+        <v>0.4434582043062379</v>
       </c>
       <c r="J16" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K16" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1349658589766949</v>
+        <v>0.1360602121087557</v>
       </c>
       <c r="M16" t="n">
-        <v>6.589643600990415</v>
+        <v>6.580830495438896</v>
       </c>
       <c r="N16" t="n">
-        <v>69.37927480551313</v>
+        <v>69.25338942699848</v>
       </c>
       <c r="O16" t="n">
-        <v>8.329422237197075</v>
+        <v>8.321862136985837</v>
       </c>
       <c r="P16" t="n">
-        <v>276.7507167555478</v>
+        <v>276.7387877026</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36185,28 +36255,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3445757399543177</v>
+        <v>0.3461643901839827</v>
       </c>
       <c r="J17" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="K17" t="n">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09500108558024667</v>
+        <v>0.09613241515273752</v>
       </c>
       <c r="M17" t="n">
-        <v>6.508813470288501</v>
+        <v>6.502643432923868</v>
       </c>
       <c r="N17" t="n">
-        <v>62.58279603268628</v>
+        <v>62.48604716623677</v>
       </c>
       <c r="O17" t="n">
-        <v>7.910928898219619</v>
+        <v>7.904811646474365</v>
       </c>
       <c r="P17" t="n">
-        <v>286.1512379665795</v>
+        <v>286.1347268553932</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36244,7 +36314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R487"/>
+  <dimension ref="A1:R488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81011,6 +81081,98 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-27 22:27:15+00:00</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>-46.60073601135008,168.8211409257723</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>-46.60033679434435,168.82044548046392</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>-46.60008715896625,168.81961379857762</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>-46.59988327120685,168.81874044727644</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>-46.599563445860795,168.81797268892478</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>-46.59922595847085,168.81722101592874</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>-46.59886860172496,168.81648743910418</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>-46.59835610745975,168.81589516360515</t>
+        </is>
+      </c>
+      <c r="J488" t="inlineStr">
+        <is>
+          <t>-46.597959469968984,168.81519736358908</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>-46.5976598098842,168.81441123344283</t>
+        </is>
+      </c>
+      <c r="L488" t="inlineStr">
+        <is>
+          <t>-46.5973820707568,168.813605135115</t>
+        </is>
+      </c>
+      <c r="M488" t="inlineStr">
+        <is>
+          <t>-46.597137898698826,168.81276846015075</t>
+        </is>
+      </c>
+      <c r="N488" t="inlineStr">
+        <is>
+          <t>-46.596857871712665,168.81196444114963</t>
+        </is>
+      </c>
+      <c r="O488" t="inlineStr">
+        <is>
+          <t>-46.59661613090806,168.81112554639793</t>
+        </is>
+      </c>
+      <c r="P488" t="inlineStr">
+        <is>
+          <t>-46.59641937419472,168.81024567365273</t>
+        </is>
+      </c>
+      <c r="Q488" t="inlineStr">
+        <is>
+          <t>-46.59617092989068,168.80941287885574</t>
+        </is>
+      </c>
+      <c r="R488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R488"/>
+  <dimension ref="A1:R489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29718,6 +29718,66 @@
         <v>299.18</v>
       </c>
       <c r="R488" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="n">
+        <v>291.04</v>
+      </c>
+      <c r="C489" t="n">
+        <v>280.27</v>
+      </c>
+      <c r="D489" t="n">
+        <v>288.16</v>
+      </c>
+      <c r="E489" t="n">
+        <v>300.23</v>
+      </c>
+      <c r="F489" t="n">
+        <v>298.68</v>
+      </c>
+      <c r="G489" t="n">
+        <v>294.93</v>
+      </c>
+      <c r="H489" t="n">
+        <v>289.02</v>
+      </c>
+      <c r="I489" t="n">
+        <v>264.12</v>
+      </c>
+      <c r="J489" t="n">
+        <v>252.19</v>
+      </c>
+      <c r="K489" t="n">
+        <v>253.61</v>
+      </c>
+      <c r="L489" t="n">
+        <v>256.42</v>
+      </c>
+      <c r="M489" t="n">
+        <v>263.96</v>
+      </c>
+      <c r="N489" t="n">
+        <v>267.39</v>
+      </c>
+      <c r="O489" t="n">
+        <v>275.66</v>
+      </c>
+      <c r="P489" t="n">
+        <v>290.31</v>
+      </c>
+      <c r="Q489" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="R489" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29734,7 +29794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B518"/>
+  <dimension ref="A1:B519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34917,6 +34977,16 @@
       </c>
       <c r="B518" t="n">
         <v>0.08</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B519" t="n">
+        <v>0.74</v>
       </c>
     </row>
   </sheetData>
@@ -35085,28 +35155,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05093920733945623</v>
+        <v>-0.05175880959571253</v>
       </c>
       <c r="J2" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K2" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001521032254514831</v>
+        <v>0.001577060093588711</v>
       </c>
       <c r="M2" t="n">
-        <v>7.865008571098281</v>
+        <v>7.852848343572014</v>
       </c>
       <c r="N2" t="n">
-        <v>94.46875167724012</v>
+        <v>94.28364476780192</v>
       </c>
       <c r="O2" t="n">
-        <v>9.719503674429067</v>
+        <v>9.709976558560886</v>
       </c>
       <c r="P2" t="n">
-        <v>294.4208338226293</v>
+        <v>294.4293688555074</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35163,28 +35233,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3839691379196973</v>
+        <v>-0.3857045719659193</v>
       </c>
       <c r="J3" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K3" t="n">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03731454287306302</v>
+        <v>0.03779306392767923</v>
       </c>
       <c r="M3" t="n">
-        <v>11.91371180241367</v>
+        <v>11.89838494482201</v>
       </c>
       <c r="N3" t="n">
-        <v>209.6696692084221</v>
+        <v>209.2750894781441</v>
       </c>
       <c r="O3" t="n">
-        <v>14.4799747654622</v>
+        <v>14.46634333472506</v>
       </c>
       <c r="P3" t="n">
-        <v>294.7022206940215</v>
+        <v>294.7204024883246</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35241,28 +35311,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6584493203406335</v>
+        <v>-0.6581221354726846</v>
       </c>
       <c r="J4" t="n">
+        <v>488</v>
+      </c>
+      <c r="K4" t="n">
         <v>487</v>
       </c>
-      <c r="K4" t="n">
-        <v>486</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1405434458921301</v>
+        <v>0.140953224129664</v>
       </c>
       <c r="M4" t="n">
-        <v>9.753482378099733</v>
+        <v>9.734597923901514</v>
       </c>
       <c r="N4" t="n">
-        <v>147.2391497944616</v>
+        <v>146.9381645887519</v>
       </c>
       <c r="O4" t="n">
-        <v>12.13421401634493</v>
+        <v>12.12180533537608</v>
       </c>
       <c r="P4" t="n">
-        <v>304.7405324621331</v>
+        <v>304.7371259309796</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35319,28 +35389,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2553927588894865</v>
+        <v>-0.2544564243188429</v>
       </c>
       <c r="J5" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K5" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08925329289126205</v>
+        <v>0.08898941914271652</v>
       </c>
       <c r="M5" t="n">
-        <v>4.211957910479698</v>
+        <v>4.207578431449368</v>
       </c>
       <c r="N5" t="n">
-        <v>36.91253185678694</v>
+        <v>36.84795453744179</v>
       </c>
       <c r="O5" t="n">
-        <v>6.075568438984696</v>
+        <v>6.070251604129914</v>
       </c>
       <c r="P5" t="n">
-        <v>304.6429830570444</v>
+        <v>304.6332324172868</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35397,28 +35467,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3177120608606369</v>
+        <v>-0.3165265372747145</v>
       </c>
       <c r="J6" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K6" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1958076456149268</v>
+        <v>0.1952015189220709</v>
       </c>
       <c r="M6" t="n">
-        <v>3.537439358571358</v>
+        <v>3.536268217925655</v>
       </c>
       <c r="N6" t="n">
-        <v>22.99222556115983</v>
+        <v>22.96284552886738</v>
       </c>
       <c r="O6" t="n">
-        <v>4.795020913526846</v>
+        <v>4.791956336285565</v>
       </c>
       <c r="P6" t="n">
-        <v>304.1150281899063</v>
+        <v>304.1026825884805</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35475,28 +35545,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3345450240153361</v>
+        <v>-0.334333740112304</v>
       </c>
       <c r="J7" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K7" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3055023669315858</v>
+        <v>0.3061588396724777</v>
       </c>
       <c r="M7" t="n">
-        <v>2.900137995169169</v>
+        <v>2.895399157436505</v>
       </c>
       <c r="N7" t="n">
-        <v>14.11070308236186</v>
+        <v>14.08235101805266</v>
       </c>
       <c r="O7" t="n">
-        <v>3.756421579423942</v>
+        <v>3.752645868990659</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2377132566639</v>
+        <v>303.235513024728</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35553,28 +35623,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4512258992902541</v>
+        <v>-0.4515257201195642</v>
       </c>
       <c r="J8" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K8" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3879895593090227</v>
+        <v>0.3893344902194136</v>
       </c>
       <c r="M8" t="n">
-        <v>3.260867982897286</v>
+        <v>3.255587668973613</v>
       </c>
       <c r="N8" t="n">
-        <v>17.81189573054201</v>
+        <v>17.77653027286588</v>
       </c>
       <c r="O8" t="n">
-        <v>4.220414165759329</v>
+        <v>4.216222275078234</v>
       </c>
       <c r="P8" t="n">
-        <v>301.681904967529</v>
+        <v>301.6850271900659</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35631,28 +35701,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2795069059166965</v>
+        <v>-0.2827986629195406</v>
       </c>
       <c r="J9" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K9" t="n">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01229391641191846</v>
+        <v>0.01263171685222464</v>
       </c>
       <c r="M9" t="n">
-        <v>13.97046711263209</v>
+        <v>13.95869916858846</v>
       </c>
       <c r="N9" t="n">
-        <v>343.3241161701031</v>
+        <v>342.7517108204239</v>
       </c>
       <c r="O9" t="n">
-        <v>18.52900742538852</v>
+        <v>18.51355478616745</v>
       </c>
       <c r="P9" t="n">
-        <v>279.5946395149554</v>
+        <v>279.6292611289304</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35709,28 +35779,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3703393426143782</v>
+        <v>-0.3741224538182242</v>
       </c>
       <c r="J10" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K10" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02250655710514993</v>
+        <v>0.02304459095239553</v>
       </c>
       <c r="M10" t="n">
-        <v>13.7070421125959</v>
+        <v>13.69644708725441</v>
       </c>
       <c r="N10" t="n">
-        <v>330.3602639111496</v>
+        <v>329.8638943985277</v>
       </c>
       <c r="O10" t="n">
-        <v>18.17581535753347</v>
+        <v>18.16215555484887</v>
       </c>
       <c r="P10" t="n">
-        <v>271.3895920317927</v>
+        <v>271.428987943968</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35787,28 +35857,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4216374390584161</v>
+        <v>-0.424902856988809</v>
       </c>
       <c r="J11" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K11" t="n">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03417725613103495</v>
+        <v>0.0348215784246263</v>
       </c>
       <c r="M11" t="n">
-        <v>12.48042406814468</v>
+        <v>12.4718322193434</v>
       </c>
       <c r="N11" t="n">
-        <v>276.3843718156426</v>
+        <v>275.9467235377143</v>
       </c>
       <c r="O11" t="n">
-        <v>16.62481193324131</v>
+        <v>16.61164421536033</v>
       </c>
       <c r="P11" t="n">
-        <v>272.8101420560832</v>
+        <v>272.8444299707336</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35865,28 +35935,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5635224622924013</v>
+        <v>-0.5664642795857254</v>
       </c>
       <c r="J12" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K12" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1500746845365575</v>
+        <v>0.1518321970965973</v>
       </c>
       <c r="M12" t="n">
-        <v>7.334785776200715</v>
+        <v>7.33908990631077</v>
       </c>
       <c r="N12" t="n">
-        <v>99.74223683648746</v>
+        <v>99.64705305592722</v>
       </c>
       <c r="O12" t="n">
-        <v>9.987103525872127</v>
+        <v>9.982337053812961</v>
       </c>
       <c r="P12" t="n">
-        <v>278.6282956607816</v>
+        <v>278.6589306512639</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35943,28 +36013,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.236914240196816</v>
+        <v>-0.2374553571353461</v>
       </c>
       <c r="J13" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K13" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05086954817813427</v>
+        <v>0.05130072615170544</v>
       </c>
       <c r="M13" t="n">
-        <v>5.838650294277969</v>
+        <v>5.829717133942649</v>
       </c>
       <c r="N13" t="n">
-        <v>58.08094477383561</v>
+        <v>57.96562130073972</v>
       </c>
       <c r="O13" t="n">
-        <v>7.621085537758752</v>
+        <v>7.613515699119541</v>
       </c>
       <c r="P13" t="n">
-        <v>271.5660557161918</v>
+        <v>271.5716907066106</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36021,28 +36091,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1079810955544874</v>
+        <v>0.1075411072402786</v>
       </c>
       <c r="J14" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K14" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0113215661004793</v>
+        <v>0.01127895823327585</v>
       </c>
       <c r="M14" t="n">
-        <v>5.935212647866041</v>
+        <v>5.925444151241614</v>
       </c>
       <c r="N14" t="n">
-        <v>56.47124037611464</v>
+        <v>56.35796347566336</v>
       </c>
       <c r="O14" t="n">
-        <v>7.514734883953967</v>
+        <v>7.507194114691811</v>
       </c>
       <c r="P14" t="n">
-        <v>265.6312199062407</v>
+        <v>265.6358017808013</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36099,28 +36169,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3990554683199034</v>
+        <v>0.3996351729346351</v>
       </c>
       <c r="J15" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K15" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1335421420819565</v>
+        <v>0.1343803359212804</v>
       </c>
       <c r="M15" t="n">
-        <v>5.805870189467774</v>
+        <v>5.796700016982322</v>
       </c>
       <c r="N15" t="n">
-        <v>57.30321027207936</v>
+        <v>57.19002627558998</v>
       </c>
       <c r="O15" t="n">
-        <v>7.569888392313282</v>
+        <v>7.5624087614721</v>
       </c>
       <c r="P15" t="n">
-        <v>263.6769358709378</v>
+        <v>263.6708990428196</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36177,28 +36247,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4434582043062379</v>
+        <v>0.4442059959967715</v>
       </c>
       <c r="J16" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K16" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1360602121087557</v>
+        <v>0.1369635365593601</v>
       </c>
       <c r="M16" t="n">
-        <v>6.580830495438896</v>
+        <v>6.570399550477148</v>
       </c>
       <c r="N16" t="n">
-        <v>69.25338942699848</v>
+        <v>69.11853303619226</v>
       </c>
       <c r="O16" t="n">
-        <v>8.321862136985837</v>
+        <v>8.313755651701117</v>
       </c>
       <c r="P16" t="n">
-        <v>276.7387877026</v>
+        <v>276.7310004782287</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36255,28 +36325,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3461643901839827</v>
+        <v>0.3473802733032336</v>
       </c>
       <c r="J17" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="K17" t="n">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09613241515273752</v>
+        <v>0.09710204439715553</v>
       </c>
       <c r="M17" t="n">
-        <v>6.502643432923868</v>
+        <v>6.494790310216491</v>
       </c>
       <c r="N17" t="n">
-        <v>62.48604716623677</v>
+        <v>62.37665714682209</v>
       </c>
       <c r="O17" t="n">
-        <v>7.904811646474365</v>
+        <v>7.897889410900997</v>
       </c>
       <c r="P17" t="n">
-        <v>286.1347268553932</v>
+        <v>286.1220651010856</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36314,7 +36384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R488"/>
+  <dimension ref="A1:R489"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81173,6 +81243,98 @@
         </is>
       </c>
     </row>
+    <row r="489">
+      <c r="A489" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-13 22:27:14+00:00</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>-46.60073974143093,168.82113752852885</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>-46.60034905027771,168.8204343180815</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>-46.600100404442415,168.8196017348065</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>-46.59988357569893,168.81874016994615</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>-46.59956306524739,168.81797303558898</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>-46.599225806226144,168.81722115459485</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>-46.59887210333875,168.81648424977584</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>-46.5983738438441,168.81587900901496</t>
+        </is>
+      </c>
+      <c r="J489" t="inlineStr">
+        <is>
+          <t>-46.59797431366814,168.8151838436413</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>-46.597676404302014,168.81439611876473</t>
+        </is>
+      </c>
+      <c r="L489" t="inlineStr">
+        <is>
+          <t>-46.597389073872314,168.81359875641013</t>
+        </is>
+      </c>
+      <c r="M489" t="inlineStr">
+        <is>
+          <t>-46.59713774645796,168.81276859881916</t>
+        </is>
+      </c>
+      <c r="N489" t="inlineStr">
+        <is>
+          <t>-46.59685513139002,168.8119669371941</t>
+        </is>
+      </c>
+      <c r="O489" t="inlineStr">
+        <is>
+          <t>-46.59660935625595,168.8111317172158</t>
+        </is>
+      </c>
+      <c r="P489" t="inlineStr">
+        <is>
+          <t>-46.596412142864125,168.81025226053652</t>
+        </is>
+      </c>
+      <c r="Q489" t="inlineStr">
+        <is>
+          <t>-46.59616423142879,168.80941898043002</t>
+        </is>
+      </c>
+      <c r="R489" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R489"/>
+  <dimension ref="A1:R491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29780,6 +29780,126 @@
       <c r="R489" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="n">
+        <v>298.82</v>
+      </c>
+      <c r="C490" t="n">
+        <v>296.47</v>
+      </c>
+      <c r="D490" t="n">
+        <v>300.6</v>
+      </c>
+      <c r="E490" t="n">
+        <v>302.72</v>
+      </c>
+      <c r="F490" t="n">
+        <v>299.23</v>
+      </c>
+      <c r="G490" t="n">
+        <v>294.98</v>
+      </c>
+      <c r="H490" t="n">
+        <v>289.11</v>
+      </c>
+      <c r="I490" t="n">
+        <v>276.49</v>
+      </c>
+      <c r="J490" t="n">
+        <v>269</v>
+      </c>
+      <c r="K490" t="n">
+        <v>267.81</v>
+      </c>
+      <c r="L490" t="n">
+        <v>265.76</v>
+      </c>
+      <c r="M490" t="n">
+        <v>263.15</v>
+      </c>
+      <c r="N490" t="n">
+        <v>263.17</v>
+      </c>
+      <c r="O490" t="n">
+        <v>274.03</v>
+      </c>
+      <c r="P490" t="n">
+        <v>287.95</v>
+      </c>
+      <c r="Q490" t="n">
+        <v>293.78</v>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="n">
+        <v>306.88</v>
+      </c>
+      <c r="C491" t="n">
+        <v>307.21</v>
+      </c>
+      <c r="D491" t="n">
+        <v>305.4</v>
+      </c>
+      <c r="E491" t="n">
+        <v>304.52</v>
+      </c>
+      <c r="F491" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="G491" t="n">
+        <v>293.67</v>
+      </c>
+      <c r="H491" t="n">
+        <v>289.23</v>
+      </c>
+      <c r="I491" t="n">
+        <v>277.32</v>
+      </c>
+      <c r="J491" t="n">
+        <v>269.21</v>
+      </c>
+      <c r="K491" t="n">
+        <v>267.38</v>
+      </c>
+      <c r="L491" t="n">
+        <v>262.05</v>
+      </c>
+      <c r="M491" t="n">
+        <v>259.99</v>
+      </c>
+      <c r="N491" t="n">
+        <v>258.31</v>
+      </c>
+      <c r="O491" t="n">
+        <v>266.99</v>
+      </c>
+      <c r="P491" t="n">
+        <v>280.72</v>
+      </c>
+      <c r="Q491" t="n">
+        <v>285.47</v>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -29794,7 +29914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B519"/>
+  <dimension ref="A1:B521"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34987,6 +35107,26 @@
       </c>
       <c r="B519" t="n">
         <v>0.74</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B520" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B521" t="n">
+        <v>-0.19</v>
       </c>
     </row>
   </sheetData>
@@ -35155,28 +35295,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.05175880959571253</v>
+        <v>-0.04386063555651058</v>
       </c>
       <c r="J2" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K2" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001577060093588711</v>
+        <v>0.001137686461375909</v>
       </c>
       <c r="M2" t="n">
-        <v>7.852848343572014</v>
+        <v>7.862497381035285</v>
       </c>
       <c r="N2" t="n">
-        <v>94.28364476780192</v>
+        <v>94.35170952982054</v>
       </c>
       <c r="O2" t="n">
-        <v>9.709976558560886</v>
+        <v>9.713480814302386</v>
       </c>
       <c r="P2" t="n">
-        <v>294.4293688555074</v>
+        <v>294.3464498647415</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35233,28 +35373,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3857045719659193</v>
+        <v>-0.3716038603506155</v>
       </c>
       <c r="J3" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K3" t="n">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03779306392767923</v>
+        <v>0.03526244906028264</v>
       </c>
       <c r="M3" t="n">
-        <v>11.89838494482201</v>
+        <v>11.91789491980058</v>
       </c>
       <c r="N3" t="n">
-        <v>209.2750894781441</v>
+        <v>209.7578446379115</v>
       </c>
       <c r="O3" t="n">
-        <v>14.46634333472506</v>
+        <v>14.48301918240501</v>
       </c>
       <c r="P3" t="n">
-        <v>294.7204024883246</v>
+        <v>294.5714840063982</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35311,28 +35451,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6581221354726846</v>
+        <v>-0.6454207820499392</v>
       </c>
       <c r="J4" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K4" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L4" t="n">
-        <v>0.140953224129664</v>
+        <v>0.1365305644800442</v>
       </c>
       <c r="M4" t="n">
-        <v>9.734597923901514</v>
+        <v>9.738193668163744</v>
       </c>
       <c r="N4" t="n">
-        <v>146.9381645887519</v>
+        <v>147.3638511030591</v>
       </c>
       <c r="O4" t="n">
-        <v>12.12180533537608</v>
+        <v>12.13935134605878</v>
       </c>
       <c r="P4" t="n">
-        <v>304.7371259309796</v>
+        <v>304.603835892463</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35389,28 +35529,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2544564243188429</v>
+        <v>-0.249820883027659</v>
       </c>
       <c r="J5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K5" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08898941914271652</v>
+        <v>0.08646654627464612</v>
       </c>
       <c r="M5" t="n">
-        <v>4.207578431449368</v>
+        <v>4.21102921789099</v>
       </c>
       <c r="N5" t="n">
-        <v>36.84795453744179</v>
+        <v>36.83415543476</v>
       </c>
       <c r="O5" t="n">
-        <v>6.070251604129914</v>
+        <v>6.069114880669174</v>
       </c>
       <c r="P5" t="n">
-        <v>304.6332324172868</v>
+        <v>304.5845780529417</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35467,28 +35607,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3165265372747145</v>
+        <v>-0.3133662543072784</v>
       </c>
       <c r="J6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K6" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1952015189220709</v>
+        <v>0.1930363861595366</v>
       </c>
       <c r="M6" t="n">
-        <v>3.536268217925655</v>
+        <v>3.537990353475154</v>
       </c>
       <c r="N6" t="n">
-        <v>22.96284552886738</v>
+        <v>22.93169314878197</v>
       </c>
       <c r="O6" t="n">
-        <v>4.791956336285565</v>
+        <v>4.788704746461404</v>
       </c>
       <c r="P6" t="n">
-        <v>304.1026825884805</v>
+        <v>304.0695142893497</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35545,28 +35685,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.334333740112304</v>
+        <v>-0.3343551160184646</v>
       </c>
       <c r="J7" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K7" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3061588396724777</v>
+        <v>0.3080667529153815</v>
       </c>
       <c r="M7" t="n">
-        <v>2.895399157436505</v>
+        <v>2.886217508152969</v>
       </c>
       <c r="N7" t="n">
-        <v>14.08235101805266</v>
+        <v>14.02659340063659</v>
       </c>
       <c r="O7" t="n">
-        <v>3.752645868990659</v>
+        <v>3.745209393430037</v>
       </c>
       <c r="P7" t="n">
-        <v>303.235513024728</v>
+        <v>303.2357426122864</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35623,28 +35763,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4515257201195642</v>
+        <v>-0.4519344882114773</v>
       </c>
       <c r="J8" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K8" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3893344902194136</v>
+        <v>0.3918840532948848</v>
       </c>
       <c r="M8" t="n">
-        <v>3.255587668973613</v>
+        <v>3.244171142647428</v>
       </c>
       <c r="N8" t="n">
-        <v>17.77653027286588</v>
+        <v>17.70502990888541</v>
       </c>
       <c r="O8" t="n">
-        <v>4.216222275078234</v>
+        <v>4.20773453403199</v>
       </c>
       <c r="P8" t="n">
-        <v>301.6850271900659</v>
+        <v>301.6893163920308</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35701,28 +35841,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2827986629195406</v>
+        <v>-0.278891508452955</v>
       </c>
       <c r="J9" t="n">
+        <v>490</v>
+      </c>
+      <c r="K9" t="n">
         <v>488</v>
       </c>
-      <c r="K9" t="n">
-        <v>486</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01263171685222464</v>
+        <v>0.01239593449949161</v>
       </c>
       <c r="M9" t="n">
-        <v>13.95869916858846</v>
+        <v>13.92058133423563</v>
       </c>
       <c r="N9" t="n">
-        <v>342.7517108204239</v>
+        <v>341.4405436078645</v>
       </c>
       <c r="O9" t="n">
-        <v>18.51355478616745</v>
+        <v>18.4781098494371</v>
       </c>
       <c r="P9" t="n">
-        <v>279.6292611289304</v>
+        <v>279.5878487549605</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35779,28 +35919,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3741224538182242</v>
+        <v>-0.3679776564820423</v>
       </c>
       <c r="J10" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K10" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02304459095239553</v>
+        <v>0.02249117930953926</v>
       </c>
       <c r="M10" t="n">
-        <v>13.69644708725441</v>
+        <v>13.67438374616058</v>
       </c>
       <c r="N10" t="n">
-        <v>329.8638943985277</v>
+        <v>328.7518838325944</v>
       </c>
       <c r="O10" t="n">
-        <v>18.16215555484887</v>
+        <v>18.13151631366209</v>
       </c>
       <c r="P10" t="n">
-        <v>271.428987943968</v>
+        <v>271.3645013031694</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35857,28 +35997,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.424902856988809</v>
+        <v>-0.4199903462847448</v>
       </c>
       <c r="J11" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K11" t="n">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0348215784246263</v>
+        <v>0.03432655400124573</v>
       </c>
       <c r="M11" t="n">
-        <v>12.4718322193434</v>
+        <v>12.44437493372997</v>
       </c>
       <c r="N11" t="n">
-        <v>275.9467235377143</v>
+        <v>274.9597765763517</v>
       </c>
       <c r="O11" t="n">
-        <v>16.61164421536033</v>
+        <v>16.58191112557149</v>
       </c>
       <c r="P11" t="n">
-        <v>272.8444299707336</v>
+        <v>272.7924491140198</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35935,28 +36075,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5664642795857254</v>
+        <v>-0.5662210472020198</v>
       </c>
       <c r="J12" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K12" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1518321970965973</v>
+        <v>0.1528598541063138</v>
       </c>
       <c r="M12" t="n">
-        <v>7.33908990631077</v>
+        <v>7.316315243785905</v>
       </c>
       <c r="N12" t="n">
-        <v>99.64705305592722</v>
+        <v>99.25462082511739</v>
       </c>
       <c r="O12" t="n">
-        <v>9.982337053812961</v>
+        <v>9.962661332451153</v>
       </c>
       <c r="P12" t="n">
-        <v>278.6589306512639</v>
+        <v>278.6563930516169</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36013,28 +36153,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2374553571353461</v>
+        <v>-0.2404299485121161</v>
       </c>
       <c r="J13" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K13" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05130072615170544</v>
+        <v>0.0529175228177523</v>
       </c>
       <c r="M13" t="n">
-        <v>5.829717133942649</v>
+        <v>5.822401654218582</v>
       </c>
       <c r="N13" t="n">
-        <v>57.96562130073972</v>
+        <v>57.79394192362049</v>
       </c>
       <c r="O13" t="n">
-        <v>7.613515699119541</v>
+        <v>7.60223269333559</v>
       </c>
       <c r="P13" t="n">
-        <v>271.5716907066106</v>
+        <v>271.6029198944631</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36091,28 +36231,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1075411072402786</v>
+        <v>0.1012898963760698</v>
       </c>
       <c r="J14" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K14" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01127895823327585</v>
+        <v>0.01006056628293905</v>
       </c>
       <c r="M14" t="n">
-        <v>5.925444151241614</v>
+        <v>5.935040198448173</v>
       </c>
       <c r="N14" t="n">
-        <v>56.35796347566336</v>
+        <v>56.39431763412612</v>
       </c>
       <c r="O14" t="n">
-        <v>7.507194114691811</v>
+        <v>7.50961501237754</v>
       </c>
       <c r="P14" t="n">
-        <v>265.6358017808013</v>
+        <v>265.701423976553</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36169,28 +36309,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3996351729346351</v>
+        <v>0.3965792278279845</v>
       </c>
       <c r="J15" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K15" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1343803359212804</v>
+        <v>0.1334180559858007</v>
       </c>
       <c r="M15" t="n">
-        <v>5.796700016982322</v>
+        <v>5.789478442198393</v>
       </c>
       <c r="N15" t="n">
-        <v>57.19002627558998</v>
+        <v>57.06526624798594</v>
       </c>
       <c r="O15" t="n">
-        <v>7.5624087614721</v>
+        <v>7.554155561542663</v>
       </c>
       <c r="P15" t="n">
-        <v>263.6708990428196</v>
+        <v>263.7029978730936</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36247,28 +36387,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4442059959967715</v>
+        <v>0.4408105740669291</v>
       </c>
       <c r="J16" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K16" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1369635365593601</v>
+        <v>0.1359972523553289</v>
       </c>
       <c r="M16" t="n">
-        <v>6.570399550477148</v>
+        <v>6.564005188972599</v>
       </c>
       <c r="N16" t="n">
-        <v>69.11853303619226</v>
+        <v>68.96137173355973</v>
       </c>
       <c r="O16" t="n">
-        <v>8.313755651701117</v>
+        <v>8.304298389000706</v>
       </c>
       <c r="P16" t="n">
-        <v>276.7310004782287</v>
+        <v>276.766662657171</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36325,28 +36465,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3473802733032336</v>
+        <v>0.342753742075543</v>
       </c>
       <c r="J17" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K17" t="n">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09710204439715553</v>
+        <v>0.09526619498891875</v>
       </c>
       <c r="M17" t="n">
-        <v>6.494790310216491</v>
+        <v>6.494129299058715</v>
       </c>
       <c r="N17" t="n">
-        <v>62.37665714682209</v>
+        <v>62.32514577742266</v>
       </c>
       <c r="O17" t="n">
-        <v>7.897889410900997</v>
+        <v>7.894627652867655</v>
       </c>
       <c r="P17" t="n">
-        <v>286.1220651010856</v>
+        <v>286.1706513181391</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36384,7 +36524,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R489"/>
+  <dimension ref="A1:R491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81335,6 +81475,190 @@
         </is>
       </c>
     </row>
+    <row r="490">
+      <c r="A490" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-07 22:27:12+00:00</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>-46.600798965963904,168.82108358855874</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>-46.60047237077824,168.82032200065473</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>-46.60019510194114,168.81951548560062</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>-46.599902530328755,168.81872290613003</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>-46.599567251994735,168.81796922228284</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>-46.59922618683792,168.81722080792957</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>-46.59887278843709,168.81648362577675</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>-46.59846800649225,168.81579324390663</t>
+        </is>
+      </c>
+      <c r="J490" t="inlineStr">
+        <is>
+          <t>-46.59810227388935,168.81506729444408</t>
+        </is>
+      </c>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>-46.59778449632424,168.81429766512522</t>
+        </is>
+      </c>
+      <c r="L490" t="inlineStr">
+        <is>
+          <t>-46.59746017069538,168.81353399859356</t>
+        </is>
+      </c>
+      <c r="M490" t="inlineStr">
+        <is>
+          <t>-46.59713158070244,168.81277421488886</t>
+        </is>
+      </c>
+      <c r="N490" t="inlineStr">
+        <is>
+          <t>-46.59682300871416,168.81199619636263</t>
+        </is>
+      </c>
+      <c r="O490" t="inlineStr">
+        <is>
+          <t>-46.59659694874601,168.81114301882198</t>
+        </is>
+      </c>
+      <c r="P490" t="inlineStr">
+        <is>
+          <t>-46.59639417871462,168.8102686237348</t>
+        </is>
+      </c>
+      <c r="Q490" t="inlineStr">
+        <is>
+          <t>-46.596129825686674,168.80945032030994</t>
+        </is>
+      </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-23 22:27:06+00:00</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>-46.60086032193966,168.82102770717722</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>-46.60055412763145,168.82024753807255</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>-46.60023164114856,168.8194822060819</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>-46.5999162324689,168.8187104262553</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>-46.59957303731808,168.81796395298608</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>-46.59921621480918,168.81722989055794</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>-46.59887370190154,168.81648279377796</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>-46.5984743245977,168.81578748924414</t>
+        </is>
+      </c>
+      <c r="J491" t="inlineStr">
+        <is>
+          <t>-46.59810387243972,168.81506583844222</t>
+        </is>
+      </c>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>-46.59778122311656,168.81430064647373</t>
+        </is>
+      </c>
+      <c r="L491" t="inlineStr">
+        <is>
+          <t>-46.597431929885374,168.81355972147296</t>
+        </is>
+      </c>
+      <c r="M491" t="inlineStr">
+        <is>
+          <t>-46.5971075266408,168.8127961244817</t>
+        </is>
+      </c>
+      <c r="N491" t="inlineStr">
+        <is>
+          <t>-46.596786014342,168.81202989289667</t>
+        </is>
+      </c>
+      <c r="O491" t="inlineStr">
+        <is>
+          <t>-46.59654336046719,168.8111918306063</t>
+        </is>
+      </c>
+      <c r="P491" t="inlineStr">
+        <is>
+          <t>-46.59633914445988,168.81031875329433</t>
+        </is>
+      </c>
+      <c r="Q491" t="inlineStr">
+        <is>
+          <t>-46.59606657085576,168.8095079384344</t>
+        </is>
+      </c>
+      <c r="R491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R491"/>
+  <dimension ref="A1:R493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29898,6 +29898,126 @@
         <v>285.47</v>
       </c>
       <c r="R491" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="n">
+        <v>308.94</v>
+      </c>
+      <c r="C492" t="n">
+        <v>308.04</v>
+      </c>
+      <c r="D492" t="n">
+        <v>305.88</v>
+      </c>
+      <c r="E492" t="n">
+        <v>304.95</v>
+      </c>
+      <c r="F492" t="n">
+        <v>300.88</v>
+      </c>
+      <c r="G492" t="n">
+        <v>294.74</v>
+      </c>
+      <c r="H492" t="n">
+        <v>290.07</v>
+      </c>
+      <c r="I492" t="n">
+        <v>277.51</v>
+      </c>
+      <c r="J492" t="n">
+        <v>269.8</v>
+      </c>
+      <c r="K492" t="n">
+        <v>267.97</v>
+      </c>
+      <c r="L492" t="n">
+        <v>262.79</v>
+      </c>
+      <c r="M492" t="n">
+        <v>260.82</v>
+      </c>
+      <c r="N492" t="n">
+        <v>262.13</v>
+      </c>
+      <c r="O492" t="n">
+        <v>268.69</v>
+      </c>
+      <c r="P492" t="n">
+        <v>283.01</v>
+      </c>
+      <c r="Q492" t="n">
+        <v>288.72</v>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:21:06+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="n">
+        <v>309.26</v>
+      </c>
+      <c r="C493" t="n">
+        <v>307.92</v>
+      </c>
+      <c r="D493" t="n">
+        <v>305.31</v>
+      </c>
+      <c r="E493" t="n">
+        <v>305.41</v>
+      </c>
+      <c r="F493" t="n">
+        <v>301.48</v>
+      </c>
+      <c r="G493" t="n">
+        <v>295.31</v>
+      </c>
+      <c r="H493" t="n">
+        <v>290.4</v>
+      </c>
+      <c r="I493" t="n">
+        <v>277.87</v>
+      </c>
+      <c r="J493" t="n">
+        <v>270.52</v>
+      </c>
+      <c r="K493" t="n">
+        <v>267.86</v>
+      </c>
+      <c r="L493" t="n">
+        <v>262.9</v>
+      </c>
+      <c r="M493" t="n">
+        <v>260.85</v>
+      </c>
+      <c r="N493" t="n">
+        <v>263.21</v>
+      </c>
+      <c r="O493" t="n">
+        <v>270.05</v>
+      </c>
+      <c r="P493" t="n">
+        <v>284.33</v>
+      </c>
+      <c r="Q493" t="n">
+        <v>289.39</v>
+      </c>
+      <c r="R493" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -29914,7 +30034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B521"/>
+  <dimension ref="A1:B523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35127,6 +35247,26 @@
       </c>
       <c r="B521" t="n">
         <v>-0.19</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B522" t="n">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B523" t="n">
+        <v>-1.12</v>
       </c>
     </row>
   </sheetData>
@@ -35295,28 +35435,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04386063555651058</v>
+        <v>-0.03111749001330973</v>
       </c>
       <c r="J2" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K2" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001137686461375909</v>
+        <v>0.0005719016258427523</v>
       </c>
       <c r="M2" t="n">
-        <v>7.862497381035285</v>
+        <v>7.899270056382771</v>
       </c>
       <c r="N2" t="n">
-        <v>94.35170952982054</v>
+        <v>94.98599328869565</v>
       </c>
       <c r="O2" t="n">
-        <v>9.713480814302386</v>
+        <v>9.746075789193087</v>
       </c>
       <c r="P2" t="n">
-        <v>294.3464498647415</v>
+        <v>294.212326973481</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35373,28 +35513,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3716038603506155</v>
+        <v>-0.3528257703498547</v>
       </c>
       <c r="J3" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K3" t="n">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03526244906028264</v>
+        <v>0.03185264659593834</v>
       </c>
       <c r="M3" t="n">
-        <v>11.91789491980058</v>
+        <v>11.96027336929097</v>
       </c>
       <c r="N3" t="n">
-        <v>209.7578446379115</v>
+        <v>211.0936181323766</v>
       </c>
       <c r="O3" t="n">
-        <v>14.48301918240501</v>
+        <v>14.52906115798184</v>
       </c>
       <c r="P3" t="n">
-        <v>294.5714840063982</v>
+        <v>294.3726486825853</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35451,28 +35591,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6454207820499392</v>
+        <v>-0.6308608376625235</v>
       </c>
       <c r="J4" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K4" t="n">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1365305644800442</v>
+        <v>0.1312249745551652</v>
       </c>
       <c r="M4" t="n">
-        <v>9.738193668163744</v>
+        <v>9.748431103425601</v>
       </c>
       <c r="N4" t="n">
-        <v>147.3638511030591</v>
+        <v>148.0955859596772</v>
       </c>
       <c r="O4" t="n">
-        <v>12.13935134605878</v>
+        <v>12.1694529852281</v>
       </c>
       <c r="P4" t="n">
-        <v>304.603835892463</v>
+        <v>304.4506190218715</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35529,28 +35669,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.249820883027659</v>
+        <v>-0.2440172374708966</v>
       </c>
       <c r="J5" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K5" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08646654627464612</v>
+        <v>0.08306599246489588</v>
       </c>
       <c r="M5" t="n">
-        <v>4.21102921789099</v>
+        <v>4.219624712550236</v>
       </c>
       <c r="N5" t="n">
-        <v>36.83415543476</v>
+        <v>36.89572605912081</v>
       </c>
       <c r="O5" t="n">
-        <v>6.069114880669174</v>
+        <v>6.074185217716102</v>
       </c>
       <c r="P5" t="n">
-        <v>304.5845780529417</v>
+        <v>304.5234927020776</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35607,28 +35747,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3133662543072784</v>
+        <v>-0.3089934641510086</v>
       </c>
       <c r="J6" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K6" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1930363861595366</v>
+        <v>0.1892581652306227</v>
       </c>
       <c r="M6" t="n">
-        <v>3.537990353475154</v>
+        <v>3.546404004726562</v>
       </c>
       <c r="N6" t="n">
-        <v>22.93169314878197</v>
+        <v>22.95867241784769</v>
       </c>
       <c r="O6" t="n">
-        <v>4.788704746461404</v>
+        <v>4.791520887760763</v>
       </c>
       <c r="P6" t="n">
-        <v>304.0695142893497</v>
+        <v>304.0234880802749</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35685,28 +35825,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3343551160184646</v>
+        <v>-0.333791501678012</v>
       </c>
       <c r="J7" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K7" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3080667529153815</v>
+        <v>0.3092135931347028</v>
       </c>
       <c r="M7" t="n">
-        <v>2.886217508152969</v>
+        <v>2.877640624943441</v>
       </c>
       <c r="N7" t="n">
-        <v>14.02659340063659</v>
+        <v>13.9719165552579</v>
       </c>
       <c r="O7" t="n">
-        <v>3.745209393430037</v>
+        <v>3.737902694728408</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2357426122864</v>
+        <v>303.2298080480122</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35763,28 +35903,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4519344882114773</v>
+        <v>-0.4514603171984369</v>
       </c>
       <c r="J8" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K8" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3918840532948848</v>
+        <v>0.3934890110701813</v>
       </c>
       <c r="M8" t="n">
-        <v>3.244171142647428</v>
+        <v>3.233590297131425</v>
       </c>
       <c r="N8" t="n">
-        <v>17.70502990888541</v>
+        <v>17.63459366804634</v>
       </c>
       <c r="O8" t="n">
-        <v>4.20773453403199</v>
+        <v>4.199356339731881</v>
       </c>
       <c r="P8" t="n">
-        <v>301.6893163920308</v>
+        <v>301.6843242266032</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35841,28 +35981,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.278891508452955</v>
+        <v>-0.2744071713724005</v>
       </c>
       <c r="J9" t="n">
+        <v>492</v>
+      </c>
+      <c r="K9" t="n">
         <v>490</v>
       </c>
-      <c r="K9" t="n">
-        <v>488</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01239593449949161</v>
+        <v>0.01210779926173988</v>
       </c>
       <c r="M9" t="n">
-        <v>13.92058133423563</v>
+        <v>13.88548698975486</v>
       </c>
       <c r="N9" t="n">
-        <v>341.4405436078645</v>
+        <v>340.170567867321</v>
       </c>
       <c r="O9" t="n">
-        <v>18.4781098494371</v>
+        <v>18.44371350534704</v>
       </c>
       <c r="P9" t="n">
-        <v>279.5878487549605</v>
+        <v>279.5401840492759</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35919,28 +36059,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3679776564820423</v>
+        <v>-0.3610943890486271</v>
       </c>
       <c r="J10" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K10" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02249117930953926</v>
+        <v>0.0218461686348117</v>
       </c>
       <c r="M10" t="n">
-        <v>13.67438374616058</v>
+        <v>13.65666847502129</v>
       </c>
       <c r="N10" t="n">
-        <v>328.7518838325944</v>
+        <v>327.7129366174677</v>
       </c>
       <c r="O10" t="n">
-        <v>18.13151631366209</v>
+        <v>18.10284332963935</v>
       </c>
       <c r="P10" t="n">
-        <v>271.3645013031694</v>
+        <v>271.2920518330196</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35997,28 +36137,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4199903462847448</v>
+        <v>-0.4148958340646061</v>
       </c>
       <c r="J11" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K11" t="n">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03432655400124573</v>
+        <v>0.0337977060337028</v>
       </c>
       <c r="M11" t="n">
-        <v>12.44437493372997</v>
+        <v>12.41791286430443</v>
       </c>
       <c r="N11" t="n">
-        <v>274.9597765763517</v>
+        <v>273.9941272076117</v>
       </c>
       <c r="O11" t="n">
-        <v>16.58191112557149</v>
+        <v>16.55276796211473</v>
       </c>
       <c r="P11" t="n">
-        <v>272.7924491140198</v>
+        <v>272.7383838943779</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36075,28 +36215,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5662210472020198</v>
+        <v>-0.5667958433582633</v>
       </c>
       <c r="J12" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K12" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1528598541063138</v>
+        <v>0.1542798839000805</v>
       </c>
       <c r="M12" t="n">
-        <v>7.316315243785905</v>
+        <v>7.290282556188155</v>
       </c>
       <c r="N12" t="n">
-        <v>99.25462082511739</v>
+        <v>98.85323756258268</v>
       </c>
       <c r="O12" t="n">
-        <v>9.962661332451153</v>
+        <v>9.942496545766696</v>
       </c>
       <c r="P12" t="n">
-        <v>278.6563930516169</v>
+        <v>278.6624421871414</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36153,28 +36293,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2404299485121161</v>
+        <v>-0.2439202611005636</v>
       </c>
       <c r="J13" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K13" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0529175228177523</v>
+        <v>0.05477258696943721</v>
       </c>
       <c r="M13" t="n">
-        <v>5.822401654218582</v>
+        <v>5.817894613160767</v>
       </c>
       <c r="N13" t="n">
-        <v>57.79394192362049</v>
+        <v>57.63536317211267</v>
       </c>
       <c r="O13" t="n">
-        <v>7.60223269333559</v>
+        <v>7.591795780453572</v>
       </c>
       <c r="P13" t="n">
-        <v>271.6029198944631</v>
+        <v>271.6396552151267</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36231,28 +36371,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1012898963760698</v>
+        <v>0.09670380953264597</v>
       </c>
       <c r="J14" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K14" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01006056628293905</v>
+        <v>0.00923810104986289</v>
       </c>
       <c r="M14" t="n">
-        <v>5.935040198448173</v>
+        <v>5.935655532848355</v>
       </c>
       <c r="N14" t="n">
-        <v>56.39431763412612</v>
+        <v>56.29813151085185</v>
       </c>
       <c r="O14" t="n">
-        <v>7.50961501237754</v>
+        <v>7.503208081271094</v>
       </c>
       <c r="P14" t="n">
-        <v>265.701423976553</v>
+        <v>265.7496878741876</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36309,28 +36449,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3965792278279845</v>
+        <v>0.3926542601384029</v>
       </c>
       <c r="J15" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K15" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1334180559858007</v>
+        <v>0.1319557711926054</v>
       </c>
       <c r="M15" t="n">
-        <v>5.789478442198393</v>
+        <v>5.786956948219635</v>
       </c>
       <c r="N15" t="n">
-        <v>57.06526624798594</v>
+        <v>56.93172188963555</v>
       </c>
       <c r="O15" t="n">
-        <v>7.554155561542663</v>
+        <v>7.545311252005152</v>
       </c>
       <c r="P15" t="n">
-        <v>263.7029978730936</v>
+        <v>263.7443023964657</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36387,28 +36527,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4408105740669291</v>
+        <v>0.4369339174466972</v>
       </c>
       <c r="J16" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K16" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1359972523553289</v>
+        <v>0.1348094084982715</v>
       </c>
       <c r="M16" t="n">
-        <v>6.564005188972599</v>
+        <v>6.560780892420407</v>
       </c>
       <c r="N16" t="n">
-        <v>68.96137173355973</v>
+        <v>68.77701593713668</v>
       </c>
       <c r="O16" t="n">
-        <v>8.304298389000706</v>
+        <v>8.293190938181557</v>
       </c>
       <c r="P16" t="n">
-        <v>276.766662657171</v>
+        <v>276.8074588487829</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36465,28 +36605,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.342753742075543</v>
+        <v>0.337751136176165</v>
       </c>
       <c r="J17" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="K17" t="n">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09526619498891875</v>
+        <v>0.09330043483242167</v>
       </c>
       <c r="M17" t="n">
-        <v>6.494129299058715</v>
+        <v>6.495447185337648</v>
       </c>
       <c r="N17" t="n">
-        <v>62.32514577742266</v>
+        <v>62.22911201243154</v>
       </c>
       <c r="O17" t="n">
-        <v>7.894627652867655</v>
+        <v>7.888543085540672</v>
       </c>
       <c r="P17" t="n">
-        <v>286.1706513181391</v>
+        <v>286.223300901506</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36524,7 +36664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R491"/>
+  <dimension ref="A1:R493"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81659,6 +81799,190 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-03 22:26:54+00:00</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>-46.60087600348664,168.82101342481826</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>-46.60056044589614,168.8202417835059</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>-46.60023529506868,168.81947887812748</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>-46.59991950575772,168.81870744495095</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>-46.59957981223584,168.81795778236076</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>-46.599224359901406,168.8172224719228</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>-46.59888009615247,168.81647696978558</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>-46.59847577091096,168.81578617191158</t>
+        </is>
+      </c>
+      <c r="J492" t="inlineStr">
+        <is>
+          <t>-46.59810836360492,168.81506174776985</t>
+        </is>
+      </c>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>-46.59778571426194,168.81429655578617</t>
+        </is>
+      </c>
+      <c r="L492" t="inlineStr">
+        <is>
+          <t>-46.59743756282375,168.81355459076607</t>
+        </is>
+      </c>
+      <c r="M492" t="inlineStr">
+        <is>
+          <t>-46.597113844638486,168.81279036974883</t>
+        </is>
+      </c>
+      <c r="N492" t="inlineStr">
+        <is>
+          <t>-46.59681509222398,168.81200340714753</t>
+        </is>
+      </c>
+      <c r="O492" t="inlineStr">
+        <is>
+          <t>-46.59655630082085,168.8111800436788</t>
+        </is>
+      </c>
+      <c r="P492" t="inlineStr">
+        <is>
+          <t>-46.59635657578264,168.8103028754783</t>
+        </is>
+      </c>
+      <c r="Q492" t="inlineStr">
+        <is>
+          <t>-46.5960913095121,168.80948540428656</t>
+        </is>
+      </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-20 22:21:06+00:00</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>-46.60087843945491,168.82101120619865</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>-46.600559532412106,168.82024261549154</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>-46.600230956038516,168.8194828300733</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>-46.5999230074154,168.81870425564819</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>-46.59958437959591,168.8179536223878</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>-46.59922869887556,168.81721851993868</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>-46.59888260817951,168.8164746817882</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>-46.59847851129391,168.81578367591283</t>
+        </is>
+      </c>
+      <c r="J493" t="inlineStr">
+        <is>
+          <t>-46.59811384434867,168.81505675576196</t>
+        </is>
+      </c>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>-46.597784876929765,168.81429731845677</t>
+        </is>
+      </c>
+      <c r="L493" t="inlineStr">
+        <is>
+          <t>-46.597438400152406,168.81355382809332</t>
+        </is>
+      </c>
+      <c r="M493" t="inlineStr">
+        <is>
+          <t>-46.59711407299983,168.8127901617464</t>
+        </is>
+      </c>
+      <c r="N493" t="inlineStr">
+        <is>
+          <t>-46.59682331319454,168.8119959190247</t>
+        </is>
+      </c>
+      <c r="O493" t="inlineStr">
+        <is>
+          <t>-46.59656665310274,168.81117061413264</t>
+        </is>
+      </c>
+      <c r="P493" t="inlineStr">
+        <is>
+          <t>-46.59636662353082,168.81029372319531</t>
+        </is>
+      </c>
+      <c r="Q493" t="inlineStr">
+        <is>
+          <t>-46.5960964094806,168.8094807587827</t>
+        </is>
+      </c>
+      <c r="R493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R493"/>
+  <dimension ref="A1:R494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30018,6 +30018,66 @@
         <v>289.39</v>
       </c>
       <c r="R493" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="n">
+        <v>308.29</v>
+      </c>
+      <c r="C494" t="n">
+        <v>305.94</v>
+      </c>
+      <c r="D494" t="n">
+        <v>305.54</v>
+      </c>
+      <c r="E494" t="n">
+        <v>305.28</v>
+      </c>
+      <c r="F494" t="n">
+        <v>300.77</v>
+      </c>
+      <c r="G494" t="n">
+        <v>294.32</v>
+      </c>
+      <c r="H494" t="n">
+        <v>289.31</v>
+      </c>
+      <c r="I494" t="n">
+        <v>275.67</v>
+      </c>
+      <c r="J494" t="n">
+        <v>268.24</v>
+      </c>
+      <c r="K494" t="n">
+        <v>265.92</v>
+      </c>
+      <c r="L494" t="n">
+        <v>261.71</v>
+      </c>
+      <c r="M494" t="n">
+        <v>260.17</v>
+      </c>
+      <c r="N494" t="n">
+        <v>262.13</v>
+      </c>
+      <c r="O494" t="n">
+        <v>269.13</v>
+      </c>
+      <c r="P494" t="n">
+        <v>283.62</v>
+      </c>
+      <c r="Q494" t="n">
+        <v>288.88</v>
+      </c>
+      <c r="R494" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30034,7 +30094,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B523"/>
+  <dimension ref="A1:B524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35267,6 +35327,16 @@
       </c>
       <c r="B523" t="n">
         <v>-1.12</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B524" t="n">
+        <v>0.71</v>
       </c>
     </row>
   </sheetData>
@@ -35435,28 +35505,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03111749001330973</v>
+        <v>-0.02514644836805221</v>
       </c>
       <c r="J2" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K2" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005719016258427523</v>
+        <v>0.0003734621917542702</v>
       </c>
       <c r="M2" t="n">
-        <v>7.899270056382771</v>
+        <v>7.916279552478427</v>
       </c>
       <c r="N2" t="n">
-        <v>94.98599328869565</v>
+        <v>95.24109221457888</v>
       </c>
       <c r="O2" t="n">
-        <v>9.746075789193087</v>
+        <v>9.759154277629742</v>
       </c>
       <c r="P2" t="n">
-        <v>294.212326973481</v>
+        <v>294.1492468625741</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35513,28 +35583,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3528257703498547</v>
+        <v>-0.3443550041570504</v>
       </c>
       <c r="J3" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K3" t="n">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03185264659593834</v>
+        <v>0.03039452757146177</v>
       </c>
       <c r="M3" t="n">
-        <v>11.96027336929097</v>
+        <v>11.97670776593739</v>
       </c>
       <c r="N3" t="n">
-        <v>211.0936181323766</v>
+        <v>211.5572534717348</v>
       </c>
       <c r="O3" t="n">
-        <v>14.52906115798184</v>
+        <v>14.5450078539592</v>
       </c>
       <c r="P3" t="n">
-        <v>294.3726486825853</v>
+        <v>294.2826192802439</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35591,28 +35661,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6308608376625235</v>
+        <v>-0.6236674815304253</v>
       </c>
       <c r="J4" t="n">
+        <v>493</v>
+      </c>
+      <c r="K4" t="n">
         <v>492</v>
       </c>
-      <c r="K4" t="n">
-        <v>491</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.1312249745551652</v>
+        <v>0.1286399864409228</v>
       </c>
       <c r="M4" t="n">
-        <v>9.748431103425601</v>
+        <v>9.753582536789901</v>
       </c>
       <c r="N4" t="n">
-        <v>148.0955859596772</v>
+        <v>148.4458687359128</v>
       </c>
       <c r="O4" t="n">
-        <v>12.1694529852281</v>
+        <v>12.18383637184581</v>
       </c>
       <c r="P4" t="n">
-        <v>304.4506190218715</v>
+        <v>304.3746370372525</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35669,28 +35739,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2440172374708966</v>
+        <v>-0.2410998510102582</v>
       </c>
       <c r="J5" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K5" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08306599246489588</v>
+        <v>0.08136947329442734</v>
       </c>
       <c r="M5" t="n">
-        <v>4.219624712550236</v>
+        <v>4.224127372397676</v>
       </c>
       <c r="N5" t="n">
-        <v>36.89572605912081</v>
+        <v>36.92777783700515</v>
       </c>
       <c r="O5" t="n">
-        <v>6.074185217716102</v>
+        <v>6.076823005239262</v>
       </c>
       <c r="P5" t="n">
-        <v>304.5234927020776</v>
+        <v>304.4926724411536</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35747,28 +35817,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3089934641510086</v>
+        <v>-0.3069873923248874</v>
       </c>
       <c r="J6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K6" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1892581652306227</v>
+        <v>0.1876126978011777</v>
       </c>
       <c r="M6" t="n">
-        <v>3.546404004726562</v>
+        <v>3.549641198741383</v>
       </c>
       <c r="N6" t="n">
-        <v>22.95867241784769</v>
+        <v>22.96264436495558</v>
       </c>
       <c r="O6" t="n">
-        <v>4.791520887760763</v>
+        <v>4.791935346491601</v>
       </c>
       <c r="P6" t="n">
-        <v>304.0234880802749</v>
+        <v>304.0022952565103</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35825,28 +35895,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.333791501678012</v>
+        <v>-0.3337851031518788</v>
       </c>
       <c r="J7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K7" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3092135931347028</v>
+        <v>0.3101610960259403</v>
       </c>
       <c r="M7" t="n">
-        <v>2.877640624943441</v>
+        <v>2.871839459344692</v>
       </c>
       <c r="N7" t="n">
-        <v>13.9719165552579</v>
+        <v>13.94357646790338</v>
       </c>
       <c r="O7" t="n">
-        <v>3.737902694728408</v>
+        <v>3.734109862859337</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2298080480122</v>
+        <v>303.22974045181</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35903,28 +35973,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4514603171984369</v>
+        <v>-0.4515797937669309</v>
       </c>
       <c r="J8" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K8" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3934890110701813</v>
+        <v>0.3946804196767157</v>
       </c>
       <c r="M8" t="n">
-        <v>3.233590297131425</v>
+        <v>3.227582295633431</v>
       </c>
       <c r="N8" t="n">
-        <v>17.63459366804634</v>
+        <v>17.59900297571086</v>
       </c>
       <c r="O8" t="n">
-        <v>4.199356339731881</v>
+        <v>4.195116562827648</v>
       </c>
       <c r="P8" t="n">
-        <v>301.6843242266032</v>
+        <v>301.685586417631</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35981,28 +36051,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2744071713724005</v>
+        <v>-0.2730023122837373</v>
       </c>
       <c r="J9" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K9" t="n">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01210779926173988</v>
+        <v>0.01203816534027868</v>
       </c>
       <c r="M9" t="n">
-        <v>13.88548698975486</v>
+        <v>13.86403626965735</v>
       </c>
       <c r="N9" t="n">
-        <v>340.170567867321</v>
+        <v>339.502051133606</v>
       </c>
       <c r="O9" t="n">
-        <v>18.44371350534704</v>
+        <v>18.42558143271484</v>
       </c>
       <c r="P9" t="n">
-        <v>279.5401840492759</v>
+        <v>279.5251969398142</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36059,28 +36129,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3610943890486271</v>
+        <v>-0.3584490347421011</v>
       </c>
       <c r="J10" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K10" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0218461686348117</v>
+        <v>0.02162283336346715</v>
       </c>
       <c r="M10" t="n">
-        <v>13.65666847502129</v>
+        <v>13.64347724312231</v>
       </c>
       <c r="N10" t="n">
-        <v>327.7129366174677</v>
+        <v>327.1360907220624</v>
       </c>
       <c r="O10" t="n">
-        <v>18.10284332963935</v>
+        <v>18.08690384565757</v>
       </c>
       <c r="P10" t="n">
-        <v>271.2920518330196</v>
+        <v>271.2641054121173</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36137,28 +36207,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4148958340646061</v>
+        <v>-0.4131696714633788</v>
       </c>
       <c r="J11" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K11" t="n">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0337977060337028</v>
+        <v>0.03366733821146328</v>
       </c>
       <c r="M11" t="n">
-        <v>12.41791286430443</v>
+        <v>12.40076834424024</v>
       </c>
       <c r="N11" t="n">
-        <v>273.9941272076117</v>
+        <v>273.4708978354774</v>
       </c>
       <c r="O11" t="n">
-        <v>16.55276796211473</v>
+        <v>16.53695551894234</v>
       </c>
       <c r="P11" t="n">
-        <v>272.7383838943779</v>
+        <v>272.7199965366113</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36215,28 +36285,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5667958433582633</v>
+        <v>-0.5675167807087255</v>
       </c>
       <c r="J12" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K12" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1542798839000805</v>
+        <v>0.1551884404816047</v>
       </c>
       <c r="M12" t="n">
-        <v>7.290282556188155</v>
+        <v>7.280101874129675</v>
       </c>
       <c r="N12" t="n">
-        <v>98.85323756258268</v>
+        <v>98.65925141565931</v>
       </c>
       <c r="O12" t="n">
-        <v>9.942496545766696</v>
+        <v>9.932736350858171</v>
       </c>
       <c r="P12" t="n">
-        <v>278.6624421871414</v>
+        <v>278.6700584140456</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36293,28 +36363,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2439202611005636</v>
+        <v>-0.2459029610640687</v>
       </c>
       <c r="J13" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K13" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05477258696943721</v>
+        <v>0.05580696453152856</v>
       </c>
       <c r="M13" t="n">
-        <v>5.817894613160767</v>
+        <v>5.816868448057988</v>
       </c>
       <c r="N13" t="n">
-        <v>57.63536317211267</v>
+        <v>57.56782619620557</v>
       </c>
       <c r="O13" t="n">
-        <v>7.591795780453572</v>
+        <v>7.587346452891523</v>
       </c>
       <c r="P13" t="n">
-        <v>271.6396552151267</v>
+        <v>271.6606011306008</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36371,28 +36441,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09670380953264597</v>
+        <v>0.09421647168089782</v>
       </c>
       <c r="J14" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K14" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L14" t="n">
-        <v>0.00923810104986289</v>
+        <v>0.008799997044136365</v>
       </c>
       <c r="M14" t="n">
-        <v>5.935655532848355</v>
+        <v>5.937020865993018</v>
       </c>
       <c r="N14" t="n">
-        <v>56.29813151085185</v>
+        <v>56.26163681614037</v>
       </c>
       <c r="O14" t="n">
-        <v>7.503208081271094</v>
+        <v>7.500775747623734</v>
       </c>
       <c r="P14" t="n">
-        <v>265.7496878741876</v>
+        <v>265.7759649556204</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36449,28 +36519,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3926542601384029</v>
+        <v>0.3906046536104916</v>
       </c>
       <c r="J15" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K15" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1319557711926054</v>
+        <v>0.1311646057111541</v>
       </c>
       <c r="M15" t="n">
-        <v>5.786956948219635</v>
+        <v>5.786082626807007</v>
       </c>
       <c r="N15" t="n">
-        <v>56.93172188963555</v>
+        <v>56.86900042756843</v>
       </c>
       <c r="O15" t="n">
-        <v>7.545311252005152</v>
+        <v>7.541153786229826</v>
       </c>
       <c r="P15" t="n">
-        <v>263.7443023964657</v>
+        <v>263.7659551355985</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36527,28 +36597,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4369339174466972</v>
+        <v>0.4349835661924232</v>
       </c>
       <c r="J16" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K16" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1348094084982715</v>
+        <v>0.134207224963254</v>
       </c>
       <c r="M16" t="n">
-        <v>6.560780892420407</v>
+        <v>6.559308389670383</v>
       </c>
       <c r="N16" t="n">
-        <v>68.77701593713668</v>
+        <v>68.68528139634468</v>
       </c>
       <c r="O16" t="n">
-        <v>8.293190938181557</v>
+        <v>8.287658378356619</v>
       </c>
       <c r="P16" t="n">
-        <v>276.8074588487829</v>
+        <v>276.8280630215112</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36605,28 +36675,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.337751136176165</v>
+        <v>0.3351974582429071</v>
       </c>
       <c r="J17" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="K17" t="n">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09330043483242167</v>
+        <v>0.09228800917229374</v>
       </c>
       <c r="M17" t="n">
-        <v>6.495447185337648</v>
+        <v>6.496396720551716</v>
       </c>
       <c r="N17" t="n">
-        <v>62.22911201243154</v>
+        <v>62.18478691095515</v>
       </c>
       <c r="O17" t="n">
-        <v>7.888543085540672</v>
+        <v>7.885733124507521</v>
       </c>
       <c r="P17" t="n">
-        <v>286.223300901506</v>
+        <v>286.2502788220801</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36664,7 +36734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R493"/>
+  <dimension ref="A1:R494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81983,6 +82053,98 @@
         </is>
       </c>
     </row>
+    <row r="494">
+      <c r="A494" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-12 22:26:45+00:00</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>-46.60087105542592,168.82101793138875</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>-46.60054445992457,168.8202563432502</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>-46.60023270687527,168.81948123542855</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>-46.599922017816496,168.81870515697292</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>-46.599578974886484,168.8179585450224</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>-46.599221162762476,168.8172253839107</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>-46.59887431087784,168.81648223911208</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>-46.598461764508194,168.8157989292345</t>
+        </is>
+      </c>
+      <c r="J494" t="inlineStr">
+        <is>
+          <t>-46.598096488659266,168.8150725637834</t>
+        </is>
+      </c>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>-46.597770109434045,168.81431076918918</t>
+        </is>
+      </c>
+      <c r="L494" t="inlineStr">
+        <is>
+          <t>-46.59742934177845,168.81356207882442</t>
+        </is>
+      </c>
+      <c r="M494" t="inlineStr">
+        <is>
+          <t>-46.597108896809004,168.81279487646745</t>
+        </is>
+      </c>
+      <c r="N494" t="inlineStr">
+        <is>
+          <t>-46.59681509222398,168.81200340714753</t>
+        </is>
+      </c>
+      <c r="O494" t="inlineStr">
+        <is>
+          <t>-46.596559650088615,168.81117699294367</t>
+        </is>
+      </c>
+      <c r="P494" t="inlineStr">
+        <is>
+          <t>-46.59636121906031,168.81029864601462</t>
+        </is>
+      </c>
+      <c r="Q494" t="inlineStr">
+        <is>
+          <t>-46.596092527415045,168.8094842949126</t>
+        </is>
+      </c>
+      <c r="R494" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R494"/>
+  <dimension ref="A1:R498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30080,6 +30080,246 @@
       <c r="R494" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="n">
+        <v>307.59</v>
+      </c>
+      <c r="C495" t="n">
+        <v>305.59</v>
+      </c>
+      <c r="D495" t="n">
+        <v>305.22</v>
+      </c>
+      <c r="E495" t="n">
+        <v>305.58</v>
+      </c>
+      <c r="F495" t="n">
+        <v>300.52</v>
+      </c>
+      <c r="G495" t="n">
+        <v>294.01</v>
+      </c>
+      <c r="H495" t="n">
+        <v>289.07</v>
+      </c>
+      <c r="I495" t="n">
+        <v>274.77</v>
+      </c>
+      <c r="J495" t="n">
+        <v>267.7</v>
+      </c>
+      <c r="K495" t="n">
+        <v>265.61</v>
+      </c>
+      <c r="L495" t="n">
+        <v>261.68</v>
+      </c>
+      <c r="M495" t="n">
+        <v>260.55</v>
+      </c>
+      <c r="N495" t="n">
+        <v>263.18</v>
+      </c>
+      <c r="O495" t="n">
+        <v>270.49</v>
+      </c>
+      <c r="P495" t="n">
+        <v>284.67</v>
+      </c>
+      <c r="Q495" t="n">
+        <v>290.24</v>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="n">
+        <v>305.68</v>
+      </c>
+      <c r="C496" t="n">
+        <v>302.08</v>
+      </c>
+      <c r="D496" t="n">
+        <v>302.44</v>
+      </c>
+      <c r="E496" t="n">
+        <v>303.11</v>
+      </c>
+      <c r="F496" t="n">
+        <v>298.21</v>
+      </c>
+      <c r="G496" t="n">
+        <v>292.48</v>
+      </c>
+      <c r="H496" t="n">
+        <v>287.61</v>
+      </c>
+      <c r="I496" t="n">
+        <v>271.79</v>
+      </c>
+      <c r="J496" t="n">
+        <v>264.85</v>
+      </c>
+      <c r="K496" t="n">
+        <v>262.42</v>
+      </c>
+      <c r="L496" t="n">
+        <v>258.87</v>
+      </c>
+      <c r="M496" t="n">
+        <v>258.56</v>
+      </c>
+      <c r="N496" t="n">
+        <v>261.42</v>
+      </c>
+      <c r="O496" t="n">
+        <v>269.14</v>
+      </c>
+      <c r="P496" t="n">
+        <v>283.44</v>
+      </c>
+      <c r="Q496" t="n">
+        <v>289.09</v>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="n">
+        <v>304</v>
+      </c>
+      <c r="C497" t="n">
+        <v>299.23</v>
+      </c>
+      <c r="D497" t="n">
+        <v>301.65</v>
+      </c>
+      <c r="E497" t="n">
+        <v>302.74</v>
+      </c>
+      <c r="F497" t="n">
+        <v>297.73</v>
+      </c>
+      <c r="G497" t="n">
+        <v>292.83</v>
+      </c>
+      <c r="H497" t="n">
+        <v>287.8</v>
+      </c>
+      <c r="I497" t="n">
+        <v>268.14</v>
+      </c>
+      <c r="J497" t="n">
+        <v>261.27</v>
+      </c>
+      <c r="K497" t="n">
+        <v>259.02</v>
+      </c>
+      <c r="L497" t="n">
+        <v>257.55</v>
+      </c>
+      <c r="M497" t="n">
+        <v>258.45</v>
+      </c>
+      <c r="N497" t="n">
+        <v>261.88</v>
+      </c>
+      <c r="O497" t="n">
+        <v>269.51</v>
+      </c>
+      <c r="P497" t="n">
+        <v>283.8</v>
+      </c>
+      <c r="Q497" t="n">
+        <v>289.89</v>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="n">
+        <v>302.01</v>
+      </c>
+      <c r="C498" t="n">
+        <v>295.57</v>
+      </c>
+      <c r="D498" t="n">
+        <v>302.16</v>
+      </c>
+      <c r="E498" t="n">
+        <v>303.24</v>
+      </c>
+      <c r="F498" t="n">
+        <v>298.31</v>
+      </c>
+      <c r="G498" t="n">
+        <v>293.74</v>
+      </c>
+      <c r="H498" t="n">
+        <v>288.55</v>
+      </c>
+      <c r="I498" t="n">
+        <v>267.42</v>
+      </c>
+      <c r="J498" t="n">
+        <v>257.56</v>
+      </c>
+      <c r="K498" t="n">
+        <v>255.33</v>
+      </c>
+      <c r="L498" t="n">
+        <v>258.79</v>
+      </c>
+      <c r="M498" t="n">
+        <v>259.48</v>
+      </c>
+      <c r="N498" t="n">
+        <v>263.07</v>
+      </c>
+      <c r="O498" t="n">
+        <v>270.67</v>
+      </c>
+      <c r="P498" t="n">
+        <v>285.17</v>
+      </c>
+      <c r="Q498" t="n">
+        <v>290.98</v>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -30094,7 +30334,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B524"/>
+  <dimension ref="A1:B528"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35337,6 +35577,46 @@
       </c>
       <c r="B524" t="n">
         <v>0.71</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B525" t="n">
+        <v>-1.14</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B526" t="n">
+        <v>0.14</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:30:00+00:00</t>
+        </is>
+      </c>
+      <c r="B527" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B528" t="n">
+        <v>0.14</v>
       </c>
     </row>
   </sheetData>
@@ -35505,28 +35785,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02514644836805221</v>
+        <v>-0.007343877749467403</v>
       </c>
       <c r="J2" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K2" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0003734621917542702</v>
+        <v>3.207824464779296e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.916279552478427</v>
+        <v>7.950415161275278</v>
       </c>
       <c r="N2" t="n">
-        <v>95.24109221457888</v>
+        <v>95.5178302636661</v>
       </c>
       <c r="O2" t="n">
-        <v>9.759154277629742</v>
+        <v>9.773322375920387</v>
       </c>
       <c r="P2" t="n">
-        <v>294.1492468625741</v>
+        <v>293.9607183260588</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35583,28 +35863,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3443550041570504</v>
+        <v>-0.3197608000039868</v>
       </c>
       <c r="J3" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K3" t="n">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03039452757146177</v>
+        <v>0.02652746843173404</v>
       </c>
       <c r="M3" t="n">
-        <v>11.97670776593739</v>
+        <v>11.9987902680855</v>
       </c>
       <c r="N3" t="n">
-        <v>211.5572534717348</v>
+        <v>211.8657559872868</v>
       </c>
       <c r="O3" t="n">
-        <v>14.5450078539592</v>
+        <v>14.55560909021972</v>
       </c>
       <c r="P3" t="n">
-        <v>294.2826192802439</v>
+        <v>294.0206095644195</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35661,28 +35941,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6236674815304253</v>
+        <v>-0.5997932730827593</v>
       </c>
       <c r="J4" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K4" t="n">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1286399864409228</v>
+        <v>0.1207030907865071</v>
       </c>
       <c r="M4" t="n">
-        <v>9.753582536789901</v>
+        <v>9.759912127259124</v>
       </c>
       <c r="N4" t="n">
-        <v>148.4458687359128</v>
+        <v>149.081807824432</v>
       </c>
       <c r="O4" t="n">
-        <v>12.18383637184581</v>
+        <v>12.20990613495583</v>
       </c>
       <c r="P4" t="n">
-        <v>304.3746370372525</v>
+        <v>304.1218150102639</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -35739,28 +36019,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2410998510102582</v>
+        <v>-0.2322553000709145</v>
       </c>
       <c r="J5" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K5" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08136947329442734</v>
+        <v>0.07670536592743871</v>
       </c>
       <c r="M5" t="n">
-        <v>4.224127372397676</v>
+        <v>4.230629755563631</v>
       </c>
       <c r="N5" t="n">
-        <v>36.92777783700515</v>
+        <v>36.88959865931422</v>
       </c>
       <c r="O5" t="n">
-        <v>6.076823005239262</v>
+        <v>6.073680816384265</v>
       </c>
       <c r="P5" t="n">
-        <v>304.4926724411536</v>
+        <v>304.399007406181</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -35817,28 +36097,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3069873923248874</v>
+        <v>-0.3024066548861096</v>
       </c>
       <c r="J6" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K6" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1876126978011777</v>
+        <v>0.1852311529942593</v>
       </c>
       <c r="M6" t="n">
-        <v>3.549641198741383</v>
+        <v>3.545075096011316</v>
       </c>
       <c r="N6" t="n">
-        <v>22.96264436495558</v>
+        <v>22.8539446733716</v>
       </c>
       <c r="O6" t="n">
-        <v>4.791935346491601</v>
+        <v>4.780579951571942</v>
       </c>
       <c r="P6" t="n">
-        <v>304.0022952565103</v>
+        <v>303.9537931774458</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -35895,28 +36175,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3337851031518788</v>
+        <v>-0.335389130572589</v>
       </c>
       <c r="J7" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K7" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3101610960259403</v>
+        <v>0.3158524802343945</v>
       </c>
       <c r="M7" t="n">
-        <v>2.871839459344692</v>
+        <v>2.855963522722992</v>
       </c>
       <c r="N7" t="n">
-        <v>13.94357646790338</v>
+        <v>13.84272307303079</v>
       </c>
       <c r="O7" t="n">
-        <v>3.734109862859337</v>
+        <v>3.720581012829957</v>
       </c>
       <c r="P7" t="n">
-        <v>303.22974045181</v>
+        <v>303.2467332739424</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -35973,28 +36253,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4515797937669309</v>
+        <v>-0.4536621688296575</v>
       </c>
       <c r="J8" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K8" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3946804196767157</v>
+        <v>0.4008986949178815</v>
       </c>
       <c r="M8" t="n">
-        <v>3.227582295633431</v>
+        <v>3.211071101927789</v>
       </c>
       <c r="N8" t="n">
-        <v>17.59900297571086</v>
+        <v>17.47385995344559</v>
       </c>
       <c r="O8" t="n">
-        <v>4.195116562827648</v>
+        <v>4.180174631931732</v>
       </c>
       <c r="P8" t="n">
-        <v>301.685586417631</v>
+        <v>301.7076479077123</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36051,28 +36331,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2730023122837373</v>
+        <v>-0.2756786393611907</v>
       </c>
       <c r="J9" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K9" t="n">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01203816534027868</v>
+        <v>0.01248687104878998</v>
       </c>
       <c r="M9" t="n">
-        <v>13.86403626965735</v>
+        <v>13.77613174283255</v>
       </c>
       <c r="N9" t="n">
-        <v>339.502051133606</v>
+        <v>336.8508849548595</v>
       </c>
       <c r="O9" t="n">
-        <v>18.42558143271484</v>
+        <v>18.3534978942669</v>
       </c>
       <c r="P9" t="n">
-        <v>279.5251969398142</v>
+        <v>279.5538845936021</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36129,28 +36409,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3584490347421011</v>
+        <v>-0.3565987042940134</v>
       </c>
       <c r="J10" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K10" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02162283336346715</v>
+        <v>0.02177053352719416</v>
       </c>
       <c r="M10" t="n">
-        <v>13.64347724312231</v>
+        <v>13.56197381740991</v>
       </c>
       <c r="N10" t="n">
-        <v>327.1360907220624</v>
+        <v>324.6304755843893</v>
       </c>
       <c r="O10" t="n">
-        <v>18.08690384565757</v>
+        <v>18.01750469916379</v>
       </c>
       <c r="P10" t="n">
-        <v>271.2641054121173</v>
+        <v>271.2445815327428</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36207,28 +36487,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4131696714633788</v>
+        <v>-0.4148525504234236</v>
       </c>
       <c r="J11" t="n">
+        <v>497</v>
+      </c>
+      <c r="K11" t="n">
         <v>493</v>
       </c>
-      <c r="K11" t="n">
-        <v>489</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.03366733821146328</v>
+        <v>0.03450279768785369</v>
       </c>
       <c r="M11" t="n">
-        <v>12.40076834424024</v>
+        <v>12.32824406730044</v>
       </c>
       <c r="N11" t="n">
-        <v>273.4708978354774</v>
+        <v>271.3792251947774</v>
       </c>
       <c r="O11" t="n">
-        <v>16.53695551894234</v>
+        <v>16.47359175149055</v>
       </c>
       <c r="P11" t="n">
-        <v>272.7199965366113</v>
+        <v>272.7380471687894</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36285,28 +36565,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5675167807087255</v>
+        <v>-0.5741755807222444</v>
       </c>
       <c r="J12" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K12" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1551884404816047</v>
+        <v>0.1604256654578029</v>
       </c>
       <c r="M12" t="n">
-        <v>7.280101874129675</v>
+        <v>7.263699220479779</v>
       </c>
       <c r="N12" t="n">
-        <v>98.65925141565931</v>
+        <v>98.02409449957089</v>
       </c>
       <c r="O12" t="n">
-        <v>9.932736350858171</v>
+        <v>9.90071181782254</v>
       </c>
       <c r="P12" t="n">
-        <v>278.6700584140456</v>
+        <v>278.7406166826423</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36363,28 +36643,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2459029610640687</v>
+        <v>-0.2550292610724832</v>
       </c>
       <c r="J13" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K13" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L13" t="n">
-        <v>0.05580696453152856</v>
+        <v>0.06050738371428221</v>
       </c>
       <c r="M13" t="n">
-        <v>5.816868448057988</v>
+        <v>5.819237011973593</v>
       </c>
       <c r="N13" t="n">
-        <v>57.56782619620557</v>
+        <v>57.37505562779707</v>
       </c>
       <c r="O13" t="n">
-        <v>7.587346452891523</v>
+        <v>7.574632375752441</v>
       </c>
       <c r="P13" t="n">
-        <v>271.6606011306008</v>
+        <v>271.7572790950301</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36441,28 +36721,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09421647168089782</v>
+        <v>0.08493409942695812</v>
       </c>
       <c r="J14" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K14" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008799997044136365</v>
+        <v>0.007254277296442124</v>
       </c>
       <c r="M14" t="n">
-        <v>5.937020865993018</v>
+        <v>5.93896913902644</v>
       </c>
       <c r="N14" t="n">
-        <v>56.26163681614037</v>
+        <v>56.08750775121342</v>
       </c>
       <c r="O14" t="n">
-        <v>7.500775747623734</v>
+        <v>7.489159348766283</v>
       </c>
       <c r="P14" t="n">
-        <v>265.7759649556204</v>
+        <v>265.8742881435464</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36519,28 +36799,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3906046536104916</v>
+        <v>0.383878706709622</v>
       </c>
       <c r="J15" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K15" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1311646057111541</v>
+        <v>0.1289421105109356</v>
       </c>
       <c r="M15" t="n">
-        <v>5.786082626807007</v>
+        <v>5.775014157563373</v>
       </c>
       <c r="N15" t="n">
-        <v>56.86900042756843</v>
+        <v>56.55856581967251</v>
       </c>
       <c r="O15" t="n">
-        <v>7.541153786229826</v>
+        <v>7.520542920539215</v>
       </c>
       <c r="P15" t="n">
-        <v>263.7659551355985</v>
+        <v>263.8371983435635</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36597,28 +36877,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4349835661924232</v>
+        <v>0.4283662998220672</v>
       </c>
       <c r="J16" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K16" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L16" t="n">
-        <v>0.134207224963254</v>
+        <v>0.132467448923145</v>
       </c>
       <c r="M16" t="n">
-        <v>6.559308389670383</v>
+        <v>6.546622081455872</v>
       </c>
       <c r="N16" t="n">
-        <v>68.68528139634468</v>
+        <v>68.27556432241157</v>
       </c>
       <c r="O16" t="n">
-        <v>8.287658378356619</v>
+        <v>8.262902899248639</v>
       </c>
       <c r="P16" t="n">
-        <v>276.8280630215112</v>
+        <v>276.8981532214606</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36675,28 +36955,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3351974582429071</v>
+        <v>0.3270542766184685</v>
       </c>
       <c r="J17" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="K17" t="n">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="L17" t="n">
-        <v>0.09228800917229374</v>
+        <v>0.08940080023749486</v>
       </c>
       <c r="M17" t="n">
-        <v>6.496396720551716</v>
+        <v>6.489061717232703</v>
       </c>
       <c r="N17" t="n">
-        <v>62.18478691095515</v>
+        <v>61.89899830484098</v>
       </c>
       <c r="O17" t="n">
-        <v>7.885733124507521</v>
+        <v>7.867591645785957</v>
       </c>
       <c r="P17" t="n">
-        <v>286.2502788220801</v>
+        <v>286.3365283115255</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -36734,7 +37014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R494"/>
+  <dimension ref="A1:R498"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82145,6 +82425,374 @@
         </is>
       </c>
     </row>
+    <row r="495">
+      <c r="A495" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:26:29+00:00</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>-46.60086572674493,168.82102278461758</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>-46.600541795595774,168.8202587698734</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>-46.600230270928485,168.81948345406465</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>-46.599924301506256,168.81870307699273</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>-46.599577071819716,168.81796027834423</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>-46.59921880296939,168.8172275332349</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>-46.598872483948945,168.81648390310966</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>-46.59845491354971,168.8158051692269</t>
+        </is>
+      </c>
+      <c r="J495" t="inlineStr">
+        <is>
+          <t>-46.59809237810088,168.81507630778694</t>
+        </is>
+      </c>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>-46.5977677496794,168.8143129185323</t>
+        </is>
+      </c>
+      <c r="L495" t="inlineStr">
+        <is>
+          <t>-46.59742911341608,168.81356228682603</t>
+        </is>
+      </c>
+      <c r="M495" t="inlineStr">
+        <is>
+          <t>-46.59711178938626,168.8127922417705</t>
+        </is>
+      </c>
+      <c r="N495" t="inlineStr">
+        <is>
+          <t>-46.596823084834256,168.81199612702815</t>
+        </is>
+      </c>
+      <c r="O495" t="inlineStr">
+        <is>
+          <t>-46.59657000237022,168.8111675633963</t>
+        </is>
+      </c>
+      <c r="P495" t="inlineStr">
+        <is>
+          <t>-46.59636921158704,168.81029136578854</t>
+        </is>
+      </c>
+      <c r="Q495" t="inlineStr">
+        <is>
+          <t>-46.596102879589566,168.80947486523175</t>
+        </is>
+      </c>
+      <c r="R495" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:17+00:00</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>-46.60085118705696,168.82103602699408</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>-46.600515076180706,168.82028310542398</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>-46.600209108638644,168.8195027284572</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>-46.599905499125924,168.81872020215775</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>-46.599559487481365,168.81797629423193</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>-46.599207156248,168.8172381411869</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>-46.59886137013092,168.81649402575925</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>-46.59843222926213,168.8158258305237</t>
+        </is>
+      </c>
+      <c r="J496" t="inlineStr">
+        <is>
+          <t>-46.5980706834848,168.8150960677961</t>
+        </is>
+      </c>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>-46.59774346704017,168.8143350359554</t>
+        </is>
+      </c>
+      <c r="L496" t="inlineStr">
+        <is>
+          <t>-46.59740772347139,168.81358176963352</t>
+        </is>
+      </c>
+      <c r="M496" t="inlineStr">
+        <is>
+          <t>-46.59709664141509,168.81280603925927</t>
+        </is>
+      </c>
+      <c r="N496" t="inlineStr">
+        <is>
+          <t>-46.59680968769671,168.81200832989367</t>
+        </is>
+      </c>
+      <c r="O496" t="inlineStr">
+        <is>
+          <t>-46.59655972620834,168.81117692360877</t>
+        </is>
+      </c>
+      <c r="P496" t="inlineStr">
+        <is>
+          <t>-46.596359848912826,168.81029989405314</t>
+        </is>
+      </c>
+      <c r="Q496" t="inlineStr">
+        <is>
+          <t>-46.596094125912636,168.80948283885917</t>
+        </is>
+      </c>
+      <c r="R496" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-14 22:26:25+00:00</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>-46.600838398219985,168.82104767473288</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>-46.60049338092471,168.82030286504101</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>-46.60020309489373,168.81950820570984</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>-46.59990268257477,168.8187227674648</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>-46.59955583359255,168.81797962220725</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>-46.599209820530774,168.81723571453162</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>-46.59886281644977,168.81649270842837</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>-46.59840444480997,168.8158511371215</t>
+        </is>
+      </c>
+      <c r="J497" t="inlineStr">
+        <is>
+          <t>-46.59804343199646,168.81512088911802</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>-46.59771758585178,168.8143586093621</t>
+        </is>
+      </c>
+      <c r="L497" t="inlineStr">
+        <is>
+          <t>-46.59739767552451,168.81359092169424</t>
+        </is>
+      </c>
+      <c r="M497" t="inlineStr">
+        <is>
+          <t>-46.597095804089996,168.8128068019343</t>
+        </is>
+      </c>
+      <c r="N497" t="inlineStr">
+        <is>
+          <t>-46.59681318922145,168.81200514050897</t>
+        </is>
+      </c>
+      <c r="O497" t="inlineStr">
+        <is>
+          <t>-46.596562542637976,168.81117435821758</t>
+        </is>
+      </c>
+      <c r="P497" t="inlineStr">
+        <is>
+          <t>-46.59636258920779,168.810297397976</t>
+        </is>
+      </c>
+      <c r="Q497" t="inlineStr">
+        <is>
+          <t>-46.59610021542711,168.8094772919882</t>
+        </is>
+      </c>
+      <c r="R497" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:19:54+00:00</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>-46.6008232495363,168.82106147174952</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>-46.60046551964272,168.8203282405255</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>-46.60020697718479,168.81950466976207</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>-46.59990648872496,168.81871930083355</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>-46.599560248708194,168.81797560090365</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>-46.59921674766569,168.81722940522675</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>-46.59886852560291,168.8164875084374</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>-46.598398964040555,168.8158561291048</t>
+        </is>
+      </c>
+      <c r="J498" t="inlineStr">
+        <is>
+          <t>-46.5980151909223,168.81514661174592</t>
+        </is>
+      </c>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>-46.597689497143804,168.8143841934157</t>
+        </is>
+      </c>
+      <c r="L498" t="inlineStr">
+        <is>
+          <t>-46.59740711450493,168.81358232430395</t>
+        </is>
+      </c>
+      <c r="M498" t="inlineStr">
+        <is>
+          <t>-46.59710364449749,168.81279966052173</t>
+        </is>
+      </c>
+      <c r="N498" t="inlineStr">
+        <is>
+          <t>-46.59682224751322,168.81199688970744</t>
+        </is>
+      </c>
+      <c r="O498" t="inlineStr">
+        <is>
+          <t>-46.59657137252508,168.81116631536773</t>
+        </is>
+      </c>
+      <c r="P498" t="inlineStr">
+        <is>
+          <t>-46.59637301755195,168.81028789901342</t>
+        </is>
+      </c>
+      <c r="Q498" t="inlineStr">
+        <is>
+          <t>-46.596108512390046,168.80946973437446</t>
+        </is>
+      </c>
+      <c r="R498" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0550/nzd0550.xlsx
+++ b/data/nzd0550/nzd0550.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R498"/>
+  <dimension ref="A1:R501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30320,6 +30320,186 @@
       <c r="R498" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="n">
+        <v>298.93</v>
+      </c>
+      <c r="C499" t="n">
+        <v>290.93</v>
+      </c>
+      <c r="D499" t="n">
+        <v>302.74</v>
+      </c>
+      <c r="E499" t="n">
+        <v>303.38</v>
+      </c>
+      <c r="F499" t="n">
+        <v>295.25</v>
+      </c>
+      <c r="G499" t="n">
+        <v>291.41</v>
+      </c>
+      <c r="H499" t="n">
+        <v>290.28</v>
+      </c>
+      <c r="I499" t="n">
+        <v>264.41</v>
+      </c>
+      <c r="J499" t="n">
+        <v>253.52</v>
+      </c>
+      <c r="K499" t="n">
+        <v>251.56</v>
+      </c>
+      <c r="L499" t="n">
+        <v>258.88</v>
+      </c>
+      <c r="M499" t="n">
+        <v>260.33</v>
+      </c>
+      <c r="N499" t="n">
+        <v>265.04</v>
+      </c>
+      <c r="O499" t="n">
+        <v>272.23</v>
+      </c>
+      <c r="P499" t="n">
+        <v>287.51</v>
+      </c>
+      <c r="Q499" t="n">
+        <v>291.31</v>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>296.76</v>
+      </c>
+      <c r="C500" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="D500" t="n">
+        <v>302.22</v>
+      </c>
+      <c r="E500" t="n">
+        <v>303.23</v>
+      </c>
+      <c r="F500" t="n">
+        <v>295.22</v>
+      </c>
+      <c r="G500" t="n">
+        <v>291.21</v>
+      </c>
+      <c r="H500" t="n">
+        <v>288.65</v>
+      </c>
+      <c r="I500" t="n">
+        <v>257.73</v>
+      </c>
+      <c r="J500" t="n">
+        <v>247.13</v>
+      </c>
+      <c r="K500" t="n">
+        <v>245.88</v>
+      </c>
+      <c r="L500" t="n">
+        <v>257.92</v>
+      </c>
+      <c r="M500" t="n">
+        <v>259.16</v>
+      </c>
+      <c r="N500" t="n">
+        <v>266.19</v>
+      </c>
+      <c r="O500" t="n">
+        <v>273.91</v>
+      </c>
+      <c r="P500" t="n">
+        <v>290.49</v>
+      </c>
+      <c r="Q500" t="n">
+        <v>292.13</v>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>296.24</v>
+      </c>
+      <c r="C501" t="n">
+        <v>285.38</v>
+      </c>
+      <c r="D501" t="n">
+        <v>299.69</v>
+      </c>
+      <c r="E501" t="n">
+        <v>300.83</v>
+      </c>
+      <c r="F501" t="n">
+        <v>293.33</v>
+      </c>
+      <c r="G501" t="n">
+        <v>289.56</v>
+      </c>
+      <c r="H501" t="n">
+        <v>286.31</v>
+      </c>
+      <c r="I501" t="n">
+        <v>257.73</v>
+      </c>
+      <c r="J501" t="n">
+        <v>247.35</v>
+      </c>
+      <c r="K501" t="n">
+        <v>245.96</v>
+      </c>
+      <c r="L501" t="n">
+        <v>256.95</v>
+      </c>
+      <c r="M501" t="n">
+        <v>258.22</v>
+      </c>
+      <c r="N501" t="n">
+        <v>264.46</v>
+      </c>
+      <c r="O501" t="n">
+        <v>271.58</v>
+      </c>
+      <c r="P501" t="n">
+        <v>289</v>
+      </c>
+      <c r="Q501" t="n">
+        <v>292.18</v>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30334,7 +30514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B528"/>
+  <dimension ref="A1:B531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35617,6 +35797,36 @@
       </c>
       <c r="B528" t="n">
         <v>0.14</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B529" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B530" t="n">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B531" t="n">
+        <v>0.82</v>
       </c>
     </row>
   </sheetData>
@@ -35785,28 +35995,28 @@
         <v>0.1904</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.007343877749467403</v>
+        <v>-0.003204533323642953</v>
       </c>
       <c r="J2" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K2" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L2" t="n">
-        <v>3.207824464779296e-05</v>
+        <v>6.183592696440421e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>7.950415161275278</v>
+        <v>7.925116318362869</v>
       </c>
       <c r="N2" t="n">
-        <v>95.5178302636661</v>
+        <v>95.02691306922233</v>
       </c>
       <c r="O2" t="n">
-        <v>9.773322375920387</v>
+        <v>9.748174858363095</v>
       </c>
       <c r="P2" t="n">
-        <v>293.9607183260588</v>
+        <v>293.9166634932399</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -35863,28 +36073,28 @@
         <v>0.1185</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3197608000039868</v>
+        <v>-0.3176268607296164</v>
       </c>
       <c r="J3" t="n">
+        <v>500</v>
+      </c>
+      <c r="K3" t="n">
         <v>497</v>
       </c>
-      <c r="K3" t="n">
-        <v>494</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02652746843173404</v>
+        <v>0.02651453715666918</v>
       </c>
       <c r="M3" t="n">
-        <v>11.9987902680855</v>
+        <v>11.93718013583733</v>
       </c>
       <c r="N3" t="n">
-        <v>211.8657559872868</v>
+        <v>210.6476360968078</v>
       </c>
       <c r="O3" t="n">
-        <v>14.55560909021972</v>
+        <v>14.51370511264466</v>
       </c>
       <c r="P3" t="n">
-        <v>294.0206095644195</v>
+        <v>293.9977775388653</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -35941,28 +36151,28 @@
         <v>0.1485</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5997932730827593</v>
+        <v>-0.5839520590207303</v>
       </c>
       <c r="J4" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K4" t="n">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1207030907865071</v>
+        <v>0.115725497142119</v>
       </c>
       <c r="M4" t="n">
-        <v>9.759912127259124</v>
+        <v>9.758086340917576</v>
       </c>
       <c r="N4" t="n">
-        <v>149.081807824432</v>
+        <v>149.2824605298929</v>
       </c>
       <c r="O4" t="n">
-        <v>12.20990613495583</v>
+        <v>12.21812017169142</v>
       </c>
       <c r="P4" t="n">
-        <v>304.1218150102639</v>
+        <v>303.9532098256361</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36019,28 +36229,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2322553000709145</v>
+        <v>-0.2271948437608826</v>
       </c>
       <c r="J5" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K5" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L5" t="n">
-        <v>0.07670536592743871</v>
+        <v>0.07432275960975143</v>
       </c>
       <c r="M5" t="n">
-        <v>4.230629755563631</v>
+        <v>4.230041254069881</v>
       </c>
       <c r="N5" t="n">
-        <v>36.88959865931422</v>
+        <v>36.78707849456647</v>
       </c>
       <c r="O5" t="n">
-        <v>6.073680816384265</v>
+        <v>6.065235238188744</v>
       </c>
       <c r="P5" t="n">
-        <v>304.399007406181</v>
+        <v>304.3451463006373</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36097,28 +36307,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3024066548861096</v>
+        <v>-0.3038281926159596</v>
       </c>
       <c r="J6" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K6" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1852311529942593</v>
+        <v>0.1885664671001106</v>
       </c>
       <c r="M6" t="n">
-        <v>3.545075096011316</v>
+        <v>3.530739801297586</v>
       </c>
       <c r="N6" t="n">
-        <v>22.8539446733716</v>
+        <v>22.73030302137063</v>
       </c>
       <c r="O6" t="n">
-        <v>4.780579951571942</v>
+        <v>4.767630755560945</v>
       </c>
       <c r="P6" t="n">
-        <v>303.9537931774458</v>
+        <v>303.9689336486949</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36175,28 +36385,28 @@
         <v>0.1351</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.335389130572589</v>
+        <v>-0.3394697437194942</v>
       </c>
       <c r="J7" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K7" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3158524802343945</v>
+        <v>0.3227740469017708</v>
       </c>
       <c r="M7" t="n">
-        <v>2.855963522722992</v>
+        <v>2.8571774216716</v>
       </c>
       <c r="N7" t="n">
-        <v>13.84272307303079</v>
+        <v>13.83559144194361</v>
       </c>
       <c r="O7" t="n">
-        <v>3.720581012829957</v>
+        <v>3.719622486482144</v>
       </c>
       <c r="P7" t="n">
-        <v>303.2467332739424</v>
+        <v>303.2901806582175</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -36253,28 +36463,28 @@
         <v>0.1724</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4536621688296575</v>
+        <v>-0.454929328771822</v>
       </c>
       <c r="J8" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K8" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4008986949178815</v>
+        <v>0.4050945345183399</v>
       </c>
       <c r="M8" t="n">
-        <v>3.211071101927789</v>
+        <v>3.200615895035688</v>
       </c>
       <c r="N8" t="n">
-        <v>17.47385995344559</v>
+        <v>17.39162032564291</v>
       </c>
       <c r="O8" t="n">
-        <v>4.180174631931732</v>
+        <v>4.170326165378784</v>
       </c>
       <c r="P8" t="n">
-        <v>301.7076479077123</v>
+        <v>301.7211529706896</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -36331,28 +36541,28 @@
         <v>0.1112</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2756786393611907</v>
+        <v>-0.2900657435346767</v>
       </c>
       <c r="J9" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K9" t="n">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01248687104878998</v>
+        <v>0.01394881283026483</v>
       </c>
       <c r="M9" t="n">
-        <v>13.77613174283255</v>
+        <v>13.76688550690624</v>
       </c>
       <c r="N9" t="n">
-        <v>336.8508849548595</v>
+        <v>335.7569829759194</v>
       </c>
       <c r="O9" t="n">
-        <v>18.3534978942669</v>
+        <v>18.32367274800331</v>
       </c>
       <c r="P9" t="n">
-        <v>279.5538845936021</v>
+        <v>279.7085585492864</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -36409,28 +36619,28 @@
         <v>0.1962</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.3565987042940134</v>
+        <v>-0.3709746582695116</v>
       </c>
       <c r="J10" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K10" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L10" t="n">
-        <v>0.02177053352719416</v>
+        <v>0.02375542136418718</v>
       </c>
       <c r="M10" t="n">
-        <v>13.56197381740991</v>
+        <v>13.54712905924216</v>
       </c>
       <c r="N10" t="n">
-        <v>324.6304755843893</v>
+        <v>323.6271749744747</v>
       </c>
       <c r="O10" t="n">
-        <v>18.01750469916379</v>
+        <v>17.9896407683554</v>
       </c>
       <c r="P10" t="n">
-        <v>271.2445815327428</v>
+        <v>271.3976450107505</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -36487,28 +36697,28 @@
         <v>0.1836</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.4148525504234236</v>
+        <v>-0.4310742877118756</v>
       </c>
       <c r="J11" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K11" t="n">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L11" t="n">
-        <v>0.03450279768785369</v>
+        <v>0.03746957821591457</v>
       </c>
       <c r="M11" t="n">
-        <v>12.32824406730044</v>
+        <v>12.33950299651475</v>
       </c>
       <c r="N11" t="n">
-        <v>271.3792251947774</v>
+        <v>270.9059716837775</v>
       </c>
       <c r="O11" t="n">
-        <v>16.47359175149055</v>
+        <v>16.45922147866592</v>
       </c>
       <c r="P11" t="n">
-        <v>272.7380471687894</v>
+        <v>272.912192200177</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -36565,28 +36775,28 @@
         <v>0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.5741755807222444</v>
+        <v>-0.5804450272666356</v>
       </c>
       <c r="J12" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K12" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1604256654578029</v>
+        <v>0.1649347682656259</v>
       </c>
       <c r="M12" t="n">
-        <v>7.263699220479779</v>
+        <v>7.259527034972382</v>
       </c>
       <c r="N12" t="n">
-        <v>98.02409449957089</v>
+        <v>97.60924994551431</v>
       </c>
       <c r="O12" t="n">
-        <v>9.90071181782254</v>
+        <v>9.879739366274512</v>
       </c>
       <c r="P12" t="n">
-        <v>278.7406166826423</v>
+        <v>278.8073655748462</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -36643,28 +36853,28 @@
         <v>0.2</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2550292610724832</v>
+        <v>-0.2616323873612861</v>
       </c>
       <c r="J13" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K13" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L13" t="n">
-        <v>0.06050738371428221</v>
+        <v>0.06406420412125202</v>
       </c>
       <c r="M13" t="n">
-        <v>5.819237011973593</v>
+        <v>5.819721545411349</v>
       </c>
       <c r="N13" t="n">
-        <v>57.37505562779707</v>
+        <v>57.22347518334578</v>
       </c>
       <c r="O13" t="n">
-        <v>7.574632375752441</v>
+        <v>7.564619962915902</v>
       </c>
       <c r="P13" t="n">
-        <v>271.7572790950301</v>
+        <v>271.8275809740948</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -36721,28 +36931,28 @@
         <v>0.2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08493409942695812</v>
+        <v>0.08151064345249733</v>
       </c>
       <c r="J14" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K14" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L14" t="n">
-        <v>0.007254277296442124</v>
+        <v>0.006766591096171837</v>
       </c>
       <c r="M14" t="n">
-        <v>5.93896913902644</v>
+        <v>5.921495339126906</v>
       </c>
       <c r="N14" t="n">
-        <v>56.08750775121342</v>
+        <v>55.80468071668724</v>
       </c>
       <c r="O14" t="n">
-        <v>7.489159348766283</v>
+        <v>7.470253055732934</v>
       </c>
       <c r="P14" t="n">
-        <v>265.8742881435464</v>
+        <v>265.9107348720996</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -36799,28 +37009,28 @@
         <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.383878706709622</v>
+        <v>0.3820154640341471</v>
       </c>
       <c r="J15" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K15" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1289421105109356</v>
+        <v>0.1292862569095967</v>
       </c>
       <c r="M15" t="n">
-        <v>5.775014157563373</v>
+        <v>5.750324416181605</v>
       </c>
       <c r="N15" t="n">
-        <v>56.55856581967251</v>
+        <v>56.24002729434436</v>
       </c>
       <c r="O15" t="n">
-        <v>7.520542920539215</v>
+        <v>7.499335123485572</v>
       </c>
       <c r="P15" t="n">
-        <v>263.8371983435635</v>
+        <v>263.8570361333233</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -36877,28 +37087,28 @@
         <v>0.1408</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4283662998220672</v>
+        <v>0.429031284823704</v>
       </c>
       <c r="J16" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K16" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L16" t="n">
-        <v>0.132467448923145</v>
+        <v>0.1343292811265685</v>
       </c>
       <c r="M16" t="n">
-        <v>6.546622081455872</v>
+        <v>6.513774673987404</v>
       </c>
       <c r="N16" t="n">
-        <v>68.27556432241157</v>
+        <v>67.87667494160152</v>
       </c>
       <c r="O16" t="n">
-        <v>8.262902899248639</v>
+        <v>8.238730177739864</v>
       </c>
       <c r="P16" t="n">
-        <v>276.8981532214606</v>
+        <v>276.8910683353413</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -36955,28 +37165,28 @@
         <v>0.1393</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3270542766184685</v>
+        <v>0.3232385720028534</v>
       </c>
       <c r="J17" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="K17" t="n">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="L17" t="n">
-        <v>0.08940080023749486</v>
+        <v>0.0884814297733304</v>
       </c>
       <c r="M17" t="n">
-        <v>6.489061717232703</v>
+        <v>6.470853927837792</v>
       </c>
       <c r="N17" t="n">
-        <v>61.89899830484098</v>
+        <v>61.59143835965189</v>
       </c>
       <c r="O17" t="n">
-        <v>7.867591645785957</v>
+        <v>7.848021302191521</v>
       </c>
       <c r="P17" t="n">
-        <v>286.3365283115255</v>
+        <v>286.3771450341275</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -37014,7 +37224,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R498"/>
+  <dimension ref="A1:R501"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82793,6 +83003,282 @@
         </is>
       </c>
     </row>
+    <row r="499">
+      <c r="A499" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:27+00:00</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>-46.600799803328556,168.8210828259105</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>-46.60043019822655,168.82036041050023</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>-46.600211392339176,168.81950064848752</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>-46.599907554447,168.81871833017675</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>-46.599536955165185,168.81799681673914</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>-46.599199011154575,168.81724555981722</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>-46.59888169471515,168.8164755137873</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>-46.59837605137673,168.81587699835706</t>
+        </is>
+      </c>
+      <c r="J499" t="inlineStr">
+        <is>
+          <t>-46.597984437831116,168.8151746223392</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>-46.59766079945963,168.81441033210908</t>
+        </is>
+      </c>
+      <c r="L499" t="inlineStr">
+        <is>
+          <t>-46.597407799592204,168.81358170029972</t>
+        </is>
+      </c>
+      <c r="M499" t="inlineStr">
+        <is>
+          <t>-46.59711011473628,168.8127937671214</t>
+        </is>
+      </c>
+      <c r="N499" t="inlineStr">
+        <is>
+          <t>-46.59683724317113,168.81198323081128</t>
+        </is>
+      </c>
+      <c r="O499" t="inlineStr">
+        <is>
+          <t>-46.59658324719976,168.81115549911715</t>
+        </is>
+      </c>
+      <c r="P499" t="inlineStr">
+        <is>
+          <t>-46.59639082946612,168.81027167449932</t>
+        </is>
+      </c>
+      <c r="Q499" t="inlineStr">
+        <is>
+          <t>-46.596111024314496,168.80946744628912</t>
+        </is>
+      </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-16 22:19:59+00:00</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>-46.60078328440666,168.8210978708762</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>-46.60038794953596,168.82039888961629</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>-46.60020743392491,168.8195042537682</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>-46.59990641260195,168.81871937016618</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>-46.59953672679708,168.81799702473745</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>-46.59919748870715,168.81724694647684</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>-46.598869286823316,168.8164868151052</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>-46.59832520199393,168.81592331277938</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>-46.59793579616801,168.8152189261568</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>-46.597617562617216,168.81444971342924</t>
+        </is>
+      </c>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>-46.59740049199455,168.81358835634424</t>
+        </is>
+      </c>
+      <c r="M500" t="inlineStr">
+        <is>
+          <t>-46.59710120864278,168.81280187921323</t>
+        </is>
+      </c>
+      <c r="N500" t="inlineStr">
+        <is>
+          <t>-46.59684599698072,168.8119752573404</t>
+        </is>
+      </c>
+      <c r="O500" t="inlineStr">
+        <is>
+          <t>-46.596596035309645,168.81114385084186</t>
+        </is>
+      </c>
+      <c r="P500" t="inlineStr">
+        <is>
+          <t>-46.596413513011015,168.8102510124955</t>
+        </is>
+      </c>
+      <c r="Q500" t="inlineStr">
+        <is>
+          <t>-46.59611726606592,168.80946176074272</t>
+        </is>
+      </c>
+      <c r="R500" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-24 22:20:38+00:00</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>-46.600779325954974,168.82110147612005</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>-46.60038794953596,168.82039888961629</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>-46.60018817471511,168.81952179483756</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>-46.59988814307988,168.8187360099916</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>-46.59952233960642,168.81801012862638</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>-46.59918492851509,168.81725838641566</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>-46.59885147426469,168.8165030390738</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>-46.59832520199393,168.81592331277938</t>
+        </is>
+      </c>
+      <c r="J501" t="inlineStr">
+        <is>
+          <t>-46.5979374708422,168.8152174008311</t>
+        </is>
+      </c>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>-46.59761817158694,168.81444915876324</t>
+        </is>
+      </c>
+      <c r="L501" t="inlineStr">
+        <is>
+          <t>-46.59739310827564,168.8135950817207</t>
+        </is>
+      </c>
+      <c r="M501" t="inlineStr">
+        <is>
+          <t>-46.59709405331932,168.81280839661838</t>
+        </is>
+      </c>
+      <c r="N501" t="inlineStr">
+        <is>
+          <t>-46.59683282820606,168.811987252213</t>
+        </is>
+      </c>
+      <c r="O501" t="inlineStr">
+        <is>
+          <t>-46.596578299418795,168.8111600058888</t>
+        </is>
+      </c>
+      <c r="P501" t="inlineStr">
+        <is>
+          <t>-46.59640217123911,168.81026134349966</t>
+        </is>
+      </c>
+      <c r="Q501" t="inlineStr">
+        <is>
+          <t>-46.5961176466605,168.809461414063</t>
+        </is>
+      </c>
+      <c r="R501" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
